--- a/docs/collaudi/REL-013/AA-01-con-dati-mancanti/distinta.xlsx
+++ b/docs/collaudi/REL-013/AA-01-con-dati-mancanti/distinta.xlsx
@@ -74,13 +74,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="000000FF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -108,12 +108,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -211,16 +211,16 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Allegata alla tavola M.02, rev. 00 del 2026-10-29. Regole della distinta cfc42a99c0fd0a1a. Quantità indicative.</t>
+          <t>Committente: Committente (dati omessi). Indirizzo: Indirizzo omesso. Allegata alla tavola M.02, rev. 00 del 29.10.2026. Regole della distinta 198e12d3f9a4df09. Quantità indicative.</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Si compilano solo le celle gialle, in € oltre IVA: prezzo unitario e importo per le sezioni B-F e H, importo a corpo per la sezione G, solo prezzo unitario per le varianti V (fuori dal totale). Righe grigie: fornite da Nove C o del Committente, non si quotano. Le righe DA DEFINIRE aspettano un dato del progettista.</t>
+          <t>Si compilano solo le celle gialle, in € oltre IVA: prezzo unitario e importo per le sezioni B-F e H, importo a corpo per la sezione G, solo prezzo unitario per le varianti V (fuori dal totale). Righe grigie: forniture escluse da questa offerta (vedi la colonna Fornitura), non si quotano. Le righe DA DEFINIRE aspettano un dato del progettista.</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>A. Apparecchiature (fornite da Nove C, posa dell'installatore)</t>
+          <t>A. Apparecchiature (posa dell'installatore; chi le fornisce: colonna Fornitura)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
@@ -896,19 +896,21 @@
           <t>conf.</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
+      <c r="D14" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>20 m in 4 tratti interi: 6 + 3,5 + 3,5 + 7 m</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -918,25 +920,31 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Curva 90° Ø200 in lamiera zincata, all'uscita del plenum</t>
+          <t>Condotto flessibile coibentato Ø200 (isolamento 25 mm, barriera vapore), confezione da 10 m</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>5</v>
+          <t>conf.</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
+        </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>lunghezza di T03 DA DEFINIRE</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Manicotto di giunzione Ø200</t>
+          <t>Curva 90° Ø200 in lamiera zincata, all'uscita del plenum</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -955,7 +963,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -963,8 +971,8 @@
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -974,7 +982,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Fascetta di serraggio Ø200 (anima e mantello)</t>
+          <t>Manicotto di giunzione Ø200</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -983,7 +991,7 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -991,8 +999,8 @@
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1002,18 +1010,16 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Nastro alluminio rinforzato 50 mm</t>
+          <t>Fascetta di serraggio Ø200 (anima e mantello)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>rotolo</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -1021,8 +1027,8 @@
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1032,18 +1038,16 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Sostegno per flessibile (fascia o collare con pendino), passo ≤ 1,2 m</t>
+          <t>Nastro alluminio rinforzato 50 mm</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
+          <t>rotolo</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1051,8 +1055,8 @@
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1062,16 +1066,18 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kit sospensione: barra filettata M10, tassello per solaio in laterocemento, antivibrante</t>
+          <t>Nastro alluminio rinforzato 50 mm</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>10</v>
+          <t>rotolo</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
+        </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -1080,11 +1086,11 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>UI-01 4, PLZ-01 4, RA-01 2</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
+          <t>lunghezza di T03 DA DEFINIRE</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1094,7 +1100,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Giunto antivibrante in tela fra unità interna e plenum di ripresa</t>
+          <t>Sostegno per flessibile (fascia o collare con pendino), passo ≤ 1,2 m</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1103,20 +1109,16 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>UI-01</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1126,16 +1128,18 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Isolamento elastomerico adesivo per raccordi e plenum</t>
+          <t>Sostegno per flessibile (fascia o collare con pendino), passo ≤ 1,2 m</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>rotolo</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>1</v>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
+        </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -1144,11 +1148,11 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>PLZ-01</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
+          <t>lunghezza di T03 DA DEFINIRE</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1158,7 +1162,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Plenum di ripresa coibentato con filtro ispezionabile, bocca 1000×250, sulla bocca di aspirazione dell'unità interna</t>
+          <t>Kit sospensione: barra filettata M10, tassello per solaio in laterocemento, antivibrante</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1167,7 +1171,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -1176,11 +1180,11 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>RA-01</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
+          <t>UI-01 4, PLZ-01 4, RA-01 2</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1190,7 +1194,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Plenum porta-bocchetta coibentato per bocchetta 400×200, attacco Ø200 laterale o dall'alto</t>
+          <t>Giunto antivibrante in tela fra unità interna e plenum di ripresa</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1199,7 +1203,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -1208,44 +1212,62 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>B1, B2, B3, B4, B5</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
+          <t>UI-01</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>C. Circuito frigorifero e unità esterna</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>B.12</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Isolamento elastomerico adesivo per raccordi e plenum</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>rotolo</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>PLZ-01</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>C.1</t>
+          <t>B.13</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Tubo rame ricotto pre-isolato Ø6,35 (1/4"), isolamento ≥ 10 mm, resistente a 120 °C</t>
+          <t>Plenum di ripresa coibentato con filtro ispezionabile, bocca 1000×250, sulla bocca di aspirazione dell'unità interna</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -1254,21 +1276,21 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>T07 stimati 8 m</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
+          <t>RA-01</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>C.2</t>
+          <t>B.14</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Manicotto a brasare Ø6,35 (1/4") (riserva, posa in tratta unica)</t>
+          <t>Plenum porta-bocchetta coibentato per bocchetta 400×200, attacco Ø200 laterale o dall'alto</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1277,95 +1299,85 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>B1, B2, B3, B4, B5</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>C.3</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Tubo rame ricotto pre-isolato Ø12,7 (1/2"), isolamento ≥ 13 mm, resistente a 120 °C</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>T08 stimati 8 m</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>C. Circuito frigorifero e unità esterna</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>C.4</t>
+          <t>C.1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Manicotto a brasare Ø12,7 (1/2") (riserva, posa in tratta unica)</t>
+          <t>Tubo rame ricotto pre-isolato Ø6,35 (1/4"), isolamento ≥ 10 mm, resistente a 120 °C</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>T07 stimati 8 m</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>C.5</t>
+          <t>C.2</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Nastro di finitura e manicotti isolanti per le giunzioni a cartella</t>
+          <t>Manicotto a brasare Ø6,35 (1/4") (riserva, posa in tratta unica)</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -1373,57 +1385,59 @@
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>C.6</t>
+          <t>C.3</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Collare di sostegno linee frigorifere in controsoffitto</t>
+          <t>Tubo rame ricotto pre-isolato Ø12,7 (1/2"), isolamento ≥ 13 mm, resistente a 120 °C</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>T08 stimati 8 m</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>C.7</t>
+          <t>C.4</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Refrigerante R32, riserva per carica aggiuntiva</t>
+          <t>Manicotto a brasare Ø12,7 (1/2") (riserva, posa in tratta unica)</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>DA DEFINIRE</t>
-        </is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -1431,114 +1445,104 @@
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>C.8</t>
+          <t>C.5</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Canalina coprilinee esterna 80×60</t>
+          <t>Nastro di finitura e manicotti isolanti per le giunzioni a cartella</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>UE-01</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>C.9</t>
+          <t>C.6</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Accessori canalina: curva 2, terminale a muro 1, giunto 2</t>
+          <t>Collare di sostegno linee frigorifere in controsoffitto</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>UE-01</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>C.10</t>
+          <t>C.7</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Staffe a parete per unità esterna, portata almeno doppia del peso della macchina, con antivibranti</t>
+          <t>Refrigerante R32, riserva per carica aggiuntiva</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>kit</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>1</v>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>DA DEFINIRE</t>
+        </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>UE-01</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>C.11</t>
+          <t>C.8</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Scarico condensa dell'unità esterna (funziona anche in caldo): raccordo e tubo Ø16 fino a pluviale o pozzetto</t>
+          <t>Canalina coprilinee esterna 80×60</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -1559,41 +1563,59 @@
           <t>UE-01</t>
         </is>
       </c>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>D. Scarico condensa</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>C.9</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Accessori canalina: curva 2, terminale a muro 1, giunto 2</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>UE-01</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>C.10</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Tubo PVC rigido Ø32</t>
+          <t>Staffe a parete per unità esterna, portata almeno doppia del peso della macchina, con antivibranti</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -1602,82 +1624,72 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>T09 stimati 7,6 m</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
+          <t>UE-01</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>D.2</t>
+          <t>C.11</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Curva 87°-90° Ø32</t>
+          <t>Scarico condensa dell'unità esterna (funziona anche in caldo): raccordo e tubo Ø16 fino a pluviale o pozzetto</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>UE-01</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>D.3</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Manicotto Ø32</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>D. Scarico condensa</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Collare per tubo condensa</t>
+          <t>Tubo PVC rigido Ø32</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
@@ -1688,51 +1700,51 @@
           <t>installatore</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>T09 stimati 7,6 m</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>D.5</t>
+          <t>D.2</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Isolamento anticondensa 9 mm per il tubo della condensa</t>
+          <t>Curva 87°-90° Ø32</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>T09 stimati 7,6 m</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>D.6</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Collante e pulitore PVC</t>
+          <t>Manicotto Ø32</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -1741,7 +1753,7 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -1749,18 +1761,18 @@
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>D.7</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Raccordo di adattamento dall'attacco condensa dell'unità interna (VP20 (Øe 26)) al tubo di scarico, con fascetta</t>
+          <t>Collare per tubo condensa</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -1769,39 +1781,35 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>UI-01</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>D.8</t>
+          <t>D.5</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Sifone ispezionabile per condensa</t>
+          <t>Isolamento anticondensa 9 mm per il tubo della condensa</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -1810,21 +1818,21 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>SIF-01</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="12" t="n"/>
+          <t>T09 stimati 7,6 m</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>D.9</t>
+          <t>D.6</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Innesto sullo scarico esistente (braga 45° o presa sul sifone di un apparecchio)</t>
+          <t>Collante e pulitore PVC</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -1840,46 +1848,60 @@
           <t>installatore</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>scarico</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="n"/>
-      <c r="H46" s="12" t="n"/>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>E. Elettrico, comando e regolazione</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>D.7</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Raccordo di adattamento dall'attacco condensa dell'unità interna (VP20 (Øe 26)) al tubo di scarico, con fascetta</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>UI-01</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>D.8</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
+          <t>Sifone ispezionabile per condensa</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
@@ -1888,30 +1910,30 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>T10 stimati 15 m</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="n"/>
-      <c r="H48" s="12" t="n"/>
+          <t>SIF-01</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>E.2</t>
+          <t>D.9</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
+          <t>Innesto sullo scarico esistente (braga 45° o presa sul sifone di un apparecchio)</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
@@ -1920,114 +1942,108 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>T11 stimati 12 m</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="n"/>
-      <c r="H49" s="12" t="n"/>
+          <t>AL-01</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>E.3</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="12" t="n"/>
-      <c r="H50" s="12" t="n"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>E. Elettrico, comando e regolazione</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
+          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="12" t="n"/>
-      <c r="H51" s="12" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>T10 stimati 15 m</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>E.5</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Scatola di derivazione IP55</t>
+          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="12" t="n"/>
-      <c r="H52" s="12" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>T11 stimati 12 m</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>E.6</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Tubo corrugato Ø25 per le linee di alimentazione</t>
+          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
@@ -2035,82 +2051,74 @@
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
-      <c r="G53" s="12" t="n"/>
-      <c r="H53" s="12" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>E.7</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Cavo di collegamento 4G1,5 a doppio isolamento, Collegamento UI-UE</t>
+          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>T12 stimati 9 m</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="n"/>
-      <c r="H54" s="12" t="n"/>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>E.8</t>
+          <t>E.5</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
+          <t>Scatola di derivazione IP55</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>T13 stimati 1,5 m; T14 stimati 3,7 m</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="n"/>
-      <c r="H55" s="12" t="n"/>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>E.9</t>
+          <t>E.6</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
+          <t>Tubo corrugato Ø25 per le linee di alimentazione</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -2119,30 +2127,26 @@
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>T15 stimati 6,5 m; T16 stimati 4,9 m; T17 stimati 5,2 m; T18 stimati 3,7 m</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="n"/>
-      <c r="H56" s="12" t="n"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="11" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>E.10</t>
+          <t>E.7</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Tubo corrugato Ø20 per bus e linee di comando</t>
+          <t>Cavo di collegamento 4G1,5 a doppio isolamento, Collegamento UI-UE</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -2151,35 +2155,39 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="12" t="n"/>
-      <c r="H57" s="12" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>T12 stimati 9 m</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>E.11</t>
+          <t>E.8</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Aggiornamento dello schema del quadro elettrico</t>
+          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>a corpo</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
@@ -2188,30 +2196,30 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>QE-01</t>
-        </is>
-      </c>
-      <c r="G58" s="12" t="n"/>
-      <c r="H58" s="12" t="n"/>
+          <t>T13 stimati 1,5 m; T14 stimati 3,7 m</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>E.12</t>
+          <t>E.9</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Sezionatore onnipolare di prossimità IP55, apertura contatti ≥ 3 mm</t>
+          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
@@ -2220,67 +2228,81 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>SZ-01</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
+          <t>T15 stimati 6,5 m; T16 stimati 4,9 m; T17 stimati 5,2 m; T18 stimati 3,7 m</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="n"/>
+      <c r="H59" s="11" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>E.13</t>
+          <t>E.10</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Scatola 503 per termostati e comandi a parete</t>
+          <t>Tubo corrugato Ø20 per bus e linee di comando</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>TZ-01, TZ-02, TZ-03, TZ-04, CF-01</t>
-        </is>
-      </c>
-      <c r="G60" s="12" t="n"/>
-      <c r="H60" s="12" t="n"/>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="11" t="n"/>
+      <c r="H60" s="11" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>F. Assistenze murarie (aperture comprese; chiusure e ripristini del Committente)</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>E.11</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Aggiornamento dello schema del quadro elettrico</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>a corpo</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>QE-01</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>E.12</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Foratura di tramezza Ø250 (o vano 450×250) per flessibili e plenum di bocchetta</t>
+          <t>Sezionatore onnipolare di prossimità IP55, apertura contatti ≥ 3 mm</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -2289,7 +2311,7 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
@@ -2298,21 +2320,21 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>assunti 1 per T02, T04, T05 (attraversamenti non dati)</t>
-        </is>
-      </c>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
+          <t>SZ-01</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>E.13</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Foratura di parete interna Ø80 per linee frigorifere e cavi</t>
+          <t>Scatola 503 per termostati e comandi a parete</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -2321,58 +2343,44 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="12" t="n"/>
-      <c r="H63" s="12" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>TZ-01, TZ-02, TZ-03, TZ-04, CF-01</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="11" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>F.3</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Foratura per lo scarico della condensa</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>assunto 1 per T09 (attraversamenti non dati)</t>
-        </is>
-      </c>
-      <c r="G64" s="12" t="n"/>
-      <c r="H64" s="12" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>F. Assistenze murarie (aperture comprese)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Carotaggio parete esterna Ø80 con guaina passante e sigillatura</t>
+          <t>Foratura di tramezza Ø250 (o vano 450×250) per flessibili e plenum di bocchetta</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -2381,7 +2389,7 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -2390,62 +2398,58 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>UE-01</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="12" t="n"/>
+          <t>assunti 1 per T02, T04, T05 (attraversamenti non dati)</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>F.5</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Traccia per la condensa fino allo scarico</t>
+          <t>Foratura di parete interna Ø80 per linee frigorifere e cavi</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>scarico</t>
-        </is>
-      </c>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="11" t="n"/>
+      <c r="H66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Tracce per le linee dal quadro al controsoffitto</t>
+          <t>Foratura per lo scarico della condensa</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
@@ -2454,21 +2458,21 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>QE-01</t>
-        </is>
-      </c>
-      <c r="G67" s="12" t="n"/>
-      <c r="H67" s="12" t="n"/>
+          <t>assunto 1 per T09 (attraversamenti non dati)</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Traccia per termostati e comandi a parete</t>
+          <t>Carotaggio parete esterna Ø80 con guaina passante e sigillatura</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -2477,7 +2481,7 @@
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
@@ -2486,144 +2490,136 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>TZ-01, TZ-02, TZ-03, TZ-04, CF-01</t>
-        </is>
-      </c>
-      <c r="G68" s="12" t="n"/>
-      <c r="H68" s="12" t="n"/>
+          <t>UE-01</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="11" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Z. Opere del Committente (escluse dall'offerta, da coordinare)</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>F.5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Traccia per la condensa fino allo scarico</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>AL-01</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="11" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Z.1</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Velette o controsoffitti per le bocchette, altezza utile ≥ 30 cm</t>
+          <t>Tracce per le linee dal quadro al controsoffitto</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>a corpo</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>committente</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>escluso</t>
-        </is>
-      </c>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>QE-01</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="11" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Z.2</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Controsoffitto in zona unità interna e plenum: altezza libera ≥ 35 cm sotto il solaio</t>
+          <t>Traccia per termostati e comandi a parete</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>a corpo</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>committente</t>
+          <t>installatore</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>UI-01</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="n"/>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>escluso</t>
-        </is>
-      </c>
+          <t>TZ-01, TZ-02, TZ-03, TZ-04, CF-01</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="11" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>Z.3</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Botola di ispezione ≥ 600×600 sotto la macchina (filtro, pompa, scheda)</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>committente</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>UI-01, PLZ-01</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="n"/>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>escluso</t>
-        </is>
-      </c>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Z. Opere del Committente (escluse dall'offerta, da coordinare)</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Z.4</t>
+          <t>Z.1</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Griglia di ripresa 1000×250 senza filtro, apribile per accedere al filtro</t>
+          <t>Velette o controsoffitti per le bocchette, altezza utile ≥ 30 cm</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>a corpo</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
@@ -2634,11 +2630,7 @@
           <t>committente</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>RA-01</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="inlineStr"/>
       <c r="G73" s="9" t="n"/>
       <c r="H73" s="10" t="inlineStr">
         <is>
@@ -2649,21 +2641,21 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Z.5</t>
+          <t>Z.2</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Bocchetta di mandata 400×200 a doppio filare con serranda</t>
+          <t>Controsoffitto in zona unità interna e plenum: altezza libera ≥ 35 cm sotto il solaio</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>a corpo</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
@@ -2672,7 +2664,7 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>B1, B2, B3, B4, B5</t>
+          <t>UI-01</t>
         </is>
       </c>
       <c r="G74" s="9" t="n"/>
@@ -2685,12 +2677,12 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Z.6</t>
+          <t>Z.3</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Griglia di transito o luce sotto porta per il ritorno dell'aria dal locale servito</t>
+          <t>Botola di ispezione ≥ 600×600 sotto la macchina (filtro, pompa, scheda)</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -2699,7 +2691,7 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
@@ -2708,7 +2700,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Aeff min.: B1 0,05 m², B2 0,052 m², B3 0,039 m², B4 0,051 m², B5 0,051 m²</t>
+          <t>UI-01, PLZ-01</t>
         </is>
       </c>
       <c r="G75" s="9" t="n"/>
@@ -2721,17 +2713,17 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Z.7</t>
+          <t>Z.4</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Chiusura e ripristino di fori, tracce e passaggi</t>
+          <t>Griglia di ripresa 1000×250 senza filtro, apribile per accedere al filtro</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>a corpo</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -2742,7 +2734,11 @@
           <t>committente</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>RA-01</t>
+        </is>
+      </c>
       <c r="G76" s="9" t="n"/>
       <c r="H76" s="10" t="inlineStr">
         <is>
@@ -2751,56 +2747,86 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>G. Attività da quotare a corpo (manodopera, mezzi, prove, documenti)</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Z.5</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Bocchetta di mandata 400×200 a doppio filare con serranda</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>committente</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>B1, B2, B3, B4, B5</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>escluso</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>Z.6</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Posa dell'unità interna in controsoffitto su sospensioni antivibranti, con plenum di zona e plenum di ripresa.</t>
+          <t>Griglia di transito o luce sotto porta per il ritorno dell'aria dal locale servito</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>a corpo</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr"/>
+          <t>committente</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Aeff min.: Camera 13 m² 0,05 m², Camera 15 m² 0,052 m², Camera 16 m² 0,039 m², Soggiorno-cucina 0,102 m²</t>
+        </is>
+      </c>
       <c r="G78" s="9" t="n"/>
-      <c r="H78" s="12" t="n"/>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>escluso</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>Z.7</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Posa dell'unità esterna su staffe con antivibranti; canalina esterna e scarico condensa dell'unità esterna.</t>
+          <t>Chiusura e ripristino di fori, tracce e passaggi</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -2813,50 +2839,40 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>installatore</t>
+          <t>committente</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="9" t="n"/>
-      <c r="H79" s="12" t="n"/>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>escluso</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>G.3</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Linee frigorifere: posa e cartelle; prova di tenuta in azoto prima della chiusura del controsoffitto, circuito lasciato in pressione con manometro fino al secondo accesso, con verbale; vuoto, apertura rubinetti, eventuale carica, registrazione F-Gas.</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>a corpo</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="12" t="n"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>G. Attività da quotare a corpo (manodopera, mezzi, prove, documenti)</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="6" t="n"/>
+      <c r="H80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Distribuzione aria: 5 rami flessibili con plenum porta-bocchetta, sostegni e sigillature; bocche protette fino alla posa delle bocchette.</t>
+          <t>Posa dell'unità interna in controsoffitto su sospensioni antivibranti, con plenum di zona e plenum di ripresa.</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -2874,17 +2890,17 @@
       </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="9" t="n"/>
-      <c r="H81" s="12" t="n"/>
+      <c r="H81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Scarico condensa con sifone e allaccio allo scarico; prova di scarico e della pompa prima della chiusura del controsoffitto.</t>
+          <t>Posa dell'unità esterna su staffe con antivibranti; canalina esterna e scarico condensa dell'unità esterna.</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -2902,17 +2918,17 @@
       </c>
       <c r="F82" s="7" t="inlineStr"/>
       <c r="G82" s="9" t="n"/>
-      <c r="H82" s="12" t="n"/>
+      <c r="H82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Linee elettriche dedicate dal quadro, collegamento fra le unità, linee di comando e bus; posa di termostati e comandi a parete.</t>
+          <t>Linee frigorifere: posa e cartelle; prova di tenuta in azoto prima della chiusura del controsoffitto, circuito lasciato in pressione con manometro fino al secondo accesso, con verbale; vuoto, apertura rubinetti, eventuale carica, registrazione F-Gas.</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -2930,17 +2946,17 @@
       </c>
       <c r="F83" s="7" t="inlineStr"/>
       <c r="G83" s="9" t="n"/>
-      <c r="H83" s="12" t="n"/>
+      <c r="H83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Messa in servizio con Nove C, al secondo accesso: regolazione della prevalenza dell'unità interna e misura delle portate per zona, configurazione della zonizzazione e dei comandi, app; collaudo con verbale.</t>
+          <t>Distribuzione aria: 5 rami flessibili con plenum porta-bocchetta, sostegni e sigillature; bocche protette fino alla posa delle bocchette.</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -2958,17 +2974,17 @@
       </c>
       <c r="F84" s="7" t="inlineStr"/>
       <c r="G84" s="9" t="n"/>
-      <c r="H84" s="12" t="n"/>
+      <c r="H84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>G.8</t>
+          <t>G.5</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Dichiarazione di conformità D.M. 37/2008, art. 1 lettera a) (impianti elettrici), con lo schema del quadro aggiornato e gli allegati.</t>
+          <t>Scarico condensa con sifone e allaccio allo scarico; prova di scarico e della pompa prima della chiusura del controsoffitto.</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -2986,17 +3002,17 @@
       </c>
       <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="9" t="n"/>
-      <c r="H85" s="12" t="n"/>
+      <c r="H85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>G.9</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Dichiarazione di conformità D.M. 37/2008, art. 1 lettera c) (impianti di climatizzazione), con allegati; documenti per libretto di impianto, catasto regionale e F-Gas.</t>
+          <t>Linee elettriche dedicate dal quadro, collegamento fra le unità, linee di comando e bus; posa di termostati e comandi a parete.</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -3014,17 +3030,17 @@
       </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="9" t="n"/>
-      <c r="H86" s="12" t="n"/>
+      <c r="H86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>G.10</t>
+          <t>G.7</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Cantiere: POS e oneri della sicurezza (presenza dell'impresa del Committente), trabattello e mezzi di sollevamento.</t>
+          <t>Messa in servizio con Nove C, al secondo accesso: regolazione della prevalenza dell'unità interna e misura delle portate per zona, configurazione della zonizzazione e dei comandi, app; collaudo con verbale.</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -3042,17 +3058,17 @@
       </c>
       <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="9" t="n"/>
-      <c r="H87" s="12" t="n"/>
+      <c r="H87" s="11" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>G.11</t>
+          <t>G.8</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Trasporto, ricevimento e custodia delle apparecchiature fornite da Nove C fino al collaudo; protezioni delle macchine e delle bocche durante le opere edili.</t>
+          <t>Dichiarazione di conformità D.M. 37/2008, art. 1 lettera a) (impianti elettrici), con lo schema del quadro aggiornato e gli allegati.</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -3070,17 +3086,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="9" t="n"/>
-      <c r="H88" s="12" t="n"/>
+      <c r="H88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>G.12</t>
+          <t>G.9</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Pulizia finale e smaltimento di imballi e residui di lavorazione.</t>
+          <t>Dichiarazione di conformità D.M. 37/2008, art. 1 lettera c) (impianti di climatizzazione), con allegati; documenti per libretto di impianto, catasto regionale e F-Gas.</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -3098,80 +3114,110 @@
       </c>
       <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="9" t="n"/>
-      <c r="H89" s="12" t="n"/>
+      <c r="H89" s="11" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>H. Voci aggiunte dall'installatore dopo il sopralluogo (necessarie per l'impianto finito)</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="6" t="n"/>
-      <c r="H90" s="6" t="n"/>
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>G.10</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Cantiere: POS e oneri della sicurezza (presenza dell'impresa del Committente), trabattello e mezzi di sollevamento.</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>a corpo</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>H.1</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr"/>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="8" t="inlineStr"/>
+          <t>G.11</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Trasporto, ricevimento e custodia delle apparecchiature fornite da Nove C fino al collaudo; protezioni delle macchine e delle bocche durante le opere edili.</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>a corpo</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="12" t="n"/>
-      <c r="H91" s="12" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="11" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>H.2</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr"/>
-      <c r="C92" s="7" t="inlineStr"/>
-      <c r="D92" s="8" t="inlineStr"/>
+          <t>G.12</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Pulizia finale e smaltimento di imballi e residui di lavorazione.</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>a corpo</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
           <t>installatore</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
-      <c r="G92" s="12" t="n"/>
-      <c r="H92" s="12" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="11" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>H.3</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr"/>
-      <c r="C93" s="7" t="inlineStr"/>
-      <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="12" t="n"/>
-      <c r="H93" s="12" t="n"/>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>H. Voci aggiunte dall'installatore dopo il sopralluogo (necessarie per l'impianto finito)</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr"/>
@@ -3183,13 +3229,13 @@
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
-      <c r="G94" s="12" t="n"/>
-      <c r="H94" s="12" t="n"/>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="11" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>H.5</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr"/>
@@ -3201,13 +3247,13 @@
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="12" t="n"/>
-      <c r="H95" s="12" t="n"/>
+      <c r="G95" s="11" t="n"/>
+      <c r="H95" s="11" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr"/>
@@ -3219,135 +3265,99 @@
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="12" t="n"/>
-      <c r="H96" s="12" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>H.4</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr"/>
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="8" t="inlineStr"/>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="11" t="n"/>
     </row>
     <row r="98">
-      <c r="F98" s="13" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>H.5</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr"/>
+      <c r="C98" s="7" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>H.6</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr"/>
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="8" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>TOTALE A CORPO, oltre IVA (somma degli importi B-H)</t>
         </is>
       </c>
-      <c r="H98" s="14" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="H101" s="14" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>V. Prezzi unitari per varianti (fuori dal prezzo a corpo, solo se Nove C le ordina per iscritto)</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>V.1</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Linea frigorifera completa oltre la quantità di computo (coppia pre-isolata, cavo di collegamento, canalina, refrigerante)</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr"/>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="12" t="n"/>
-      <c r="H101" s="10" t="inlineStr">
-        <is>
-          <t>variante, fuori totale</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>V.2</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Flessibile posato oltre la quantità di computo, con fascette e sostegni</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr"/>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr"/>
-      <c r="G102" s="12" t="n"/>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>variante, fuori totale</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>V.3</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Cavo di alimentazione in corrugato oltre la quantità di computo, stessa sezione</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr"/>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>installatore</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr"/>
-      <c r="G103" s="12" t="n"/>
-      <c r="H103" s="10" t="inlineStr">
-        <is>
-          <t>variante, fuori totale</t>
-        </is>
-      </c>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="n"/>
+      <c r="H103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>V.4</t>
+          <t>V.1</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Accesso aggiuntivo in cantiere (oltre i due previsti)</t>
+          <t>Linea frigorifera completa oltre la quantità di computo (coppia pre-isolata, cavo di collegamento, canalina, refrigerante)</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr"/>
@@ -3357,7 +3367,7 @@
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="12" t="n"/>
+      <c r="G104" s="11" t="n"/>
       <c r="H104" s="10" t="inlineStr">
         <is>
           <t>variante, fuori totale</t>
@@ -3367,17 +3377,17 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>V.5</t>
+          <t>V.2</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Centralino aggiuntivo 8 moduli, se il quadro non ha i moduli liberi per le protezioni nuove</t>
+          <t>Flessibile posato oltre la quantità di computo, con fascette e sostegni</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr"/>
@@ -3387,48 +3397,138 @@
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
-      <c r="G105" s="12" t="n"/>
+      <c r="G105" s="11" t="n"/>
       <c r="H105" s="10" t="inlineStr">
         <is>
           <t>variante, fuori totale</t>
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>V.3</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione in corrugato oltre la quantità di computo, stessa sezione</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="11" t="n"/>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>variante, fuori totale</t>
+        </is>
+      </c>
+    </row>
     <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>V.4</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Accesso aggiuntivo in cantiere (oltre i due previsti)</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="11" t="n"/>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>variante, fuori totale</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>V.5</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Centralino aggiuntivo 8 moduli, se il quadro non ha i moduli liberi per le protezioni nuove</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>installatore</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="11" t="n"/>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>variante, fuori totale</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
         <is>
           <t>Validità dell'offerta, tempi di esecuzione (posa prima della chiusura del controsoffitto, messa in servizio al secondo accesso) e referente tecnico dell'installatore:</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="40" customHeight="1">
-      <c r="A108" s="16" t="n"/>
-      <c r="B108" s="17" t="n"/>
-      <c r="C108" s="17" t="n"/>
-      <c r="D108" s="17" t="n"/>
-      <c r="E108" s="17" t="n"/>
-      <c r="F108" s="17" t="n"/>
-      <c r="G108" s="17" t="n"/>
-      <c r="H108" s="18" t="n"/>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="16" t="n"/>
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="17" t="n"/>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="17" t="n"/>
+      <c r="F111" s="17" t="n"/>
+      <c r="G111" s="17" t="n"/>
+      <c r="H111" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A107:H107"/>
-    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A103:H103"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A108:H108"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3864,7 +3964,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>UI-01 - SIF-01 - scarico</t>
+          <t>UI-01 - SIF-01 - AL-01</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3904,7 +4004,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>UE-01 - SZ-01 - QE-01</t>
+          <t>QE-01 - SZ-01 - UE-01</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -4262,7 +4362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4340,7 +4440,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §2, proposta 5 approvata dal PO («flessibili ≤ 3 m/s»); proposta 3 (flessibili Ø200 a 2,4-2,6 m/s)</t>
+          <t>regola Nove C per il comfort acustico (mandata fino a 3 m/s)</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4472,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §2, proposta 5 approvata dal PO («flessibili ≤ 3 m/s»); proposta 3 (flessibili Ø200 a 2,4-2,6 m/s)</t>
+          <t>regola Nove C per il comfort acustico (mandata fino a 3 m/s)</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4504,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §2, proposta 5 approvata dal PO («flessibili ≤ 3 m/s»); proposta 3 (flessibili Ø200 a 2,4-2,6 m/s)</t>
+          <t>regola Nove C per il comfort acustico (mandata fino a 3 m/s)</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4536,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §2, proposta 5 approvata dal PO («flessibili ≤ 3 m/s»); proposta 3 (flessibili Ø200 a 2,4-2,6 m/s)</t>
+          <t>regola Nove C per il comfort acustico (mandata fino a 3 m/s)</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4568,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §2, proposta 5 approvata dal PO («flessibili ≤ 3 m/s»); proposta 3 (flessibili Ø200 a 2,4-2,6 m/s)</t>
+          <t>regola Nove C per il comfort acustico (mandata fino a 3 m/s)</t>
         </is>
       </c>
     </row>
@@ -4500,14 +4600,14 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §2, proposta 5 («ripresa &lt; 2 m/s»), sulla sezione lorda; REVISIONE-INDIPENDENTE.md rilievo 4 (1,9 m/s lordi diventano ~3 m/s reali con griglia e filtro)</t>
+          <t>regola Nove C per il comfort acustico (ripresa fino a 2 m/s)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>Camera 13 m²</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4532,14 +4632,14 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («griglie di transito a 1,5 m/s»)</t>
+          <t>regola Nove C per il ritorno dell'aria (1,5 m/s nelle griglie di transito)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Camera 15 m²</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4564,14 +4664,14 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («griglie di transito a 1,5 m/s»)</t>
+          <t>regola Nove C per il ritorno dell'aria (1,5 m/s nelle griglie di transito)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Camera 16 m²</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4596,14 +4696,14 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («griglie di transito a 1,5 m/s»)</t>
+          <t>regola Nove C per il ritorno dell'aria (1,5 m/s nelle griglie di transito)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>Soggiorno-cucina</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4613,12 +4713,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>275 m³/h a 1,5 m/s</t>
+          <t>550 m³/h a 1,5 m/s</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Aeff ≥ 0,051 m²</t>
+          <t>Aeff ≥ 0,102 m²</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -4628,46 +4728,46 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («griglie di transito a 1,5 m/s»)</t>
+          <t>regola Nove C per il ritorno dell'aria (1,5 m/s nelle griglie di transito)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>griglia di transito</t>
+          <t>lunghezza della linea frigorifera</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>275 m³/h a 1,5 m/s</t>
+          <t>12 m da quotare</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Aeff ≥ 0,051 m²</t>
+          <t>≤ 30 m (UE-01)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>da rispettare</t>
+          <t>entro</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («griglie di transito a 1,5 m/s»)</t>
+          <t>scheda tecnica dell'unità esterna (lunghezza massima della linea)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4692,29 +4792,29 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (massimo 30 m dalla scheda Daikin RXM-A, citata in RAPPORTO.md §10)</t>
+          <t>scheda tecnica dell'unità esterna (lunghezza massima della linea)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>lunghezza della linea frigorifera</t>
+          <t>scritta sulla tavola</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>12 m da quotare</t>
+          <t>«Ø200 · 270 m³/h · L 6 m»</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>≤ 30 m (UE-01)</t>
+          <t>L 6 m da quotare</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -4724,14 +4824,14 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (massimo 30 m dalla scheda Daikin RXM-A, citata in RAPPORTO.md §10)</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4741,12 +4841,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>«Ø200 · 270 m³/h · L 6 m»</t>
+          <t>«Ø200 · 280 m³/h · L 3,5 m»</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>L 6 m da quotare</t>
+          <t>L 3,5 m da quotare</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -4756,14 +4856,14 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4773,7 +4873,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>«Ø200 · 280 m³/h · L 3,5 m»</t>
+          <t>«Ø200 · 275 m³/h · L 3,5 m»</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -4788,14 +4888,14 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4805,12 +4905,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>«Ø200 · 275 m³/h · L 3,5 m»</t>
+          <t>«Ø200 · 275 m³/h · L 7 m»</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>L 3,5 m da quotare</t>
+          <t>L 7 m da quotare</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -4820,14 +4920,14 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4837,12 +4937,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>«Ø200 · 275 m³/h · L 7 m»</t>
+          <t>«Ø6,35 (1/4") · L 12 m»</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>L 7 m da quotare</t>
+          <t>L 12 m da quotare</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -4852,14 +4952,14 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4869,7 +4969,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>«Ø6,35 (1/4") · L 12 m»</t>
+          <t>«Ø12,7 (1/2") · L 12 m»</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -4884,14 +4984,14 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -4901,12 +5001,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>«Ø12,7 (1/2") · L 12 m»</t>
+          <t>«PVC Ø32 · L 10 m»</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>L 12 m da quotare</t>
+          <t>L 10 m da quotare</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -4916,14 +5016,14 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -4933,12 +5033,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>«PVC Ø32 · L 10 m»</t>
+          <t>«3G2,5 · L 20 m»</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>L 10 m da quotare</t>
+          <t>L 20 m da quotare</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -4948,14 +5048,14 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -4965,12 +5065,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>«3G2,5 · L 20 m»</t>
+          <t>«3G1,5 · L 15 m»</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>L 20 m da quotare</t>
+          <t>L 15 m da quotare</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -4980,14 +5080,14 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -4997,12 +5097,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>«3G1,5 · L 15 m»</t>
+          <t>«4G1,5 · L 13 m»</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>L 15 m da quotare</t>
+          <t>L 13 m da quotare</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -5012,14 +5112,14 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5029,29 +5129,29 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>«4G1,5 · L 13 m»</t>
+          <t>«P1-P2 · L 3 m»</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>L 13 m da quotare</t>
+          <t>L 5 m da quotare</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>entro</t>
+          <t>oltre</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5061,29 +5161,29 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>«P1-P2 · L 3 m»</t>
+          <t>«P1-P2 · L 5,5 m»</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>L 5 m da quotare</t>
+          <t>L 5,5 m da quotare</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>oltre</t>
+          <t>entro</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5093,12 +5193,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>«P1-P2 · L 5,5 m»</t>
+          <t>«bus · L 9 m»</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>L 5,5 m da quotare</t>
+          <t>L 9 m da quotare</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -5108,14 +5208,14 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5125,12 +5225,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 9 m»</t>
+          <t>«bus · L 7 m»</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>L 9 m da quotare</t>
+          <t>L 7 m da quotare</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -5140,14 +5240,14 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5157,12 +5257,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 7 m»</t>
+          <t>«bus · L 7,5 m»</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>L 7 m da quotare</t>
+          <t>L 7,5 m da quotare</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -5172,14 +5272,14 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5189,12 +5289,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 7,5 m»</t>
+          <t>«bus · L 5,5 m»</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>L 7,5 m da quotare</t>
+          <t>L 5,5 m da quotare</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -5204,39 +5304,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>T18</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>scritta sulla tavola</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>«bus · L 5,5 m»</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>L 5,5 m da quotare</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>entro</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>contratto con REL-012: la scritta di un tratto («Ø200 · L 6 m») è un dato del progettista</t>
+          <t>confronto con la scritta della tratta sulla tavola</t>
         </is>
       </c>
     </row>
@@ -5251,20 +5319,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Da dove viene ogni quantità — la regola, il conto, la fonte, il perché</t>
+          <t>Da dove viene ogni quantità — la voce, il conto, la fonte, il perché</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5344,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Regola</t>
+          <t>Voce</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5303,17 +5371,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>corredo/split-outdoor-unit/apparecchiatura</t>
+          <t>Unità esterna split a pompa di calore: Daikin RXM60A · 49 kg</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>1 nel grafo (UE-01)</t>
+          <t>1 nello schema (UE-01)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voci A.1, C.5, C.6, C.8, C.9, F.1; REVISIONE-INDIPENDENTE.md rilievo 18</t>
+          <t>regola Nove C per la posa dell'unità esterna</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -5330,17 +5398,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>corredo/ducted-indoor-unit/apparecchiatura</t>
+          <t>Unità interna canalizzata ad espansione diretta: Daikin FBA60A9 · 1000×800×245 mm · 35 kg</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>1 nel grafo (UI-01)</t>
+          <t>1 nello schema (UI-01)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voci A.2, B.4, B.10, D.2, Z.1, Z.2; REVISIONE-INDIPENDENTE.md rilievi 4, 6</t>
+          <t>regola Nove C per la posa dell'unità interna canalizzata</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5357,17 +5425,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>corredo/zoning-plenum-5/apparecchiatura</t>
+          <t>Plenum motorizzato di zona a cinque serrande: Airzone Easyzone 5 × Ø200, es. AZEZ8DAIBS07M5 · 1425×250×454 mm</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>1 nel grafo (PLZ-01)</t>
+          <t>1 nello schema (PLZ-01)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voci A.3, B.10, B.11, Z.2</t>
+          <t>regola Nove C per la posa del plenum di zona</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -5384,17 +5452,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>corredo/room-thermostat/apparecchiatura</t>
+          <t>Termostato di zona: Airzone Blueface</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>4 nel grafo (TZ-01, TZ-02, TZ-03, TZ-04)</t>
+          <t>4 nello schema (TZ-01, TZ-02, TZ-03, TZ-04)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voci A.4, E.13, F.7</t>
+          <t>regola Nove C per gli apparecchi a parete</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -5411,17 +5479,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>corredo/wired-remote/apparecchiatura</t>
+          <t>Comando a filo dell'unità: Daikin Madoka BRC1H52W</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>1 nel grafo (CF-01)</t>
+          <t>1 nello schema (CF-01)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voci A.5, E.13, F.7</t>
+          <t>regola Nove C per gli apparecchi a parete</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -5438,17 +5506,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/flessibile-in-confezioni</t>
+          <t>Condotto flessibile coibentato Ø200 (isolamento 25 mm, barriera vapore), confezione da 10 m</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>manca la lunghezza di T03</t>
+          <t>4 pezzi interi, 20 m: in confezioni da 10 m (utili 9,5) ne servono 3 [7] [6 + 3,5] [3,5]; riserva 25%: 20 × 1,25 = 25 m → 3; si prende il maggiore: 3</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py (confezioni da 10 m, 0,5 m di sfrido, almeno 1,25 × la lunghezza); REVISIONE-INDIPENDENTE.md rilievo 17</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -5465,22 +5533,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/curva-in-lamiera</t>
+          <t>Condotto flessibile coibentato Ø200 (isolamento 25 mm, barriera vapore), confezione da 10 m</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>5 tratti × 1 = 5</t>
+          <t>manca la lunghezza di T03; la parte nota (T01, T02, T04, T05) e' nella riga sopra</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py (4 curve alle uscite con cambio di direzione stretto, scritte a mano sul caso)</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Il flessibile non si piega stretto all'uscita del plenum senza schiacciarsi: una curva rigida per ramo, in dubbio per eccesso (il kit ne contava una per le sole uscite strette).</t>
+          <t>Ogni ramo è un pezzo intero, senza giunte: le giunte del flessibile perdono aria e rumore. I pezzi si mettono nelle confezioni dal più lungo (first-fit decreasing); la riserva del 25% copre i tagli sbagliati e la ricollocazione di una bocchetta.</t>
         </is>
       </c>
     </row>
@@ -5492,22 +5560,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/manicotto-di-riserva</t>
+          <t>Curva 90° Ø200 in lamiera zincata, all'uscita del plenum</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>2 per sezione</t>
+          <t>5 tratti × 1 = 5</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py («Manicotto di giunzione Ø200», n 2, riserva)</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Riserva per una riparazione o un ramo da allungare in cantiere.</t>
+          <t>Il flessibile non si piega stretto all'uscita del plenum senza schiacciarsi: una curva rigida per ramo, in dubbio per eccesso (il kit ne contava una per le sole uscite strette).</t>
         </is>
       </c>
     </row>
@@ -5519,22 +5587,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/fascette</t>
+          <t>Manicotto di giunzione Ø200</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>5 tratti × 8 = 40</t>
+          <t>2 per sezione</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: REVISIONE-INDIPENDENTE.md rilievo 17 («fascette ≥ 32 con le curve»); lavoro/dimensionamento.py, 36 fascette</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Per ramo: le due estremità del flessibile e le due giunzioni della curva, ciascuna con una fascetta sull'anima e una sul mantello isolante: 4 × 2 = 8.</t>
+          <t>Riserva per una riparazione o un ramo da allungare in cantiere.</t>
         </is>
       </c>
     </row>
@@ -5546,22 +5614,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/nastro-alluminio</t>
+          <t>Fascetta di serraggio Ø200 (anima e mantello)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>manca la lunghezza di T03</t>
+          <t>5 tratti × 8 = 40</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py (2 rotoli per 26 m di flessibile); il passo di 20 m è della sessione di sviluppo, che riproduce il kit: da confermare</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>La sigillatura di giunzioni, curve e plenum.</t>
+          <t>Per ramo: le due estremità del flessibile e le due giunzioni della curva, ciascuna con una fascetta sull'anima e una sul mantello isolante: 4 × 2 = 8.</t>
         </is>
       </c>
     </row>
@@ -5573,22 +5641,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/sostegni</t>
+          <t>Nastro alluminio rinforzato 50 mm</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>manca la lunghezza di T03</t>
+          <t>20 m / 20 m per eccesso, almeno 1 = 1</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («sostegni ogni ≤ 1,2 m»); lavoro/dimensionamento.py, 25 sostegni</t>
+          <t>stima Nove C (un rotolo ogni 20 m di flessibile)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Un flessibile che si imbarca fra due sostegni perde portata e fa condensa nelle anse: un sostegno ogni 1,2 m per tratto, più uno vicino all'attacco.</t>
+          <t>La sigillatura di giunzioni, curve e plenum.</t>
         </is>
       </c>
     </row>
@@ -5600,22 +5668,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>corredo/ducted-indoor-unit/kit-sospensione + corredo/zoning-plenum-5/kit-sospensione + corredo/return-air-terminal/kit-sospensione</t>
+          <t>Nastro alluminio rinforzato 50 mm</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>UI-01 4 + PLZ-01 4 + RA-01 2 = 10</t>
+          <t>manca la lunghezza di T03; la parte nota (T01, T02, T04, T05) e' nella riga sopra</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 («kit sospensione: UI 4, plenum 4, ripresa 2»)</t>
+          <t>stima Nove C (un rotolo ogni 20 m di flessibile)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Quattro punti di sospensione per la macchina, con antivibrante.</t>
+          <t>La sigillatura di giunzioni, curve e plenum.</t>
         </is>
       </c>
     </row>
@@ -5627,22 +5695,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>corredo/ducted-indoor-unit/giunto-antivibrante-ripresa</t>
+          <t>Sostegno per flessibile (fascia o collare con pendino), passo ≤ 1,2 m</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>UI-01: 1</t>
+          <t>T01 6 + T02 4 + T04 4 + T05 7 = 21 (L / 1,2 m per eccesso +1 per tratto)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce B.4</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>La vibrazione del ventilatore non deve passare al plenum di ripresa e alla griglia.</t>
+          <t>Un flessibile che si imbarca fra due sostegni perde portata e fa condensa nelle anse: un sostegno ogni 1,2 m per tratto, più uno vicino all'attacco.</t>
         </is>
       </c>
     </row>
@@ -5654,22 +5722,22 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>corredo/zoning-plenum-5/isolamento-raccordi-plenum</t>
+          <t>Sostegno per flessibile (fascia o collare con pendino), passo ≤ 1,2 m</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>PLZ-01: 1</t>
+          <t>manca la lunghezza di T03; la parte nota (T01, T02, T04, T05) e' nella riga sopra</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce B.11</t>
+          <t>regola Nove C per i canali flessibili</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>I raccordi rigidi fra macchina, plenum e curve fanno condensa se non si isolano.</t>
+          <t>Un flessibile che si imbarca fra due sostegni perde portata e fa condensa nelle anse: un sostegno ogni 1,2 m per tratto, più uno vicino all'attacco.</t>
         </is>
       </c>
     </row>
@@ -5681,22 +5749,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>corredo/return-air-terminal/plenum-di-ripresa</t>
+          <t>Kit sospensione: barra filettata M10, tassello per solaio in laterocemento, antivibrante</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>RA-01: 1</t>
+          <t>UI-01 4 + PLZ-01 4 + RA-01 2 = 10</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce B.3; REVISIONE-INDIPENDENTE.md rilievo 4 (un solo filtro, nel plenum)</t>
+          <t>regola Nove C per la posa dell'unità interna canalizzata; regola Nove C per la posa del plenum di zona; regola Nove C per la ripresa dell'aria</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Un filtro solo, ispezionabile: due filtri in serie (plenum e griglia) raddoppiano la perdita.</t>
+          <t>Quattro punti di sospensione per la macchina, con antivibrante.</t>
         </is>
       </c>
     </row>
@@ -5708,304 +5776,304 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>corredo/air-supply-terminal/plenum-porta-bocchetta</t>
+          <t>Giunto antivibrante in tela fra unità interna e plenum di ripresa</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>5 pezzi × 1 = 5 (B1, B2, B3, B4, B5)</t>
+          <t>UI-01: 1</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce B.2; REVISIONE-INDIPENDENTE.md rilievo 5 («il plenum da ordinare sulle bocchette scelte non si può prezzare»)</t>
+          <t>regola Nove C per la posa dell'unità interna canalizzata</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Il plenum si ordina sulla misura della bocchetta: è un dato del progettista sul pezzo (`dimensione`).</t>
+          <t>La vibrazione del ventilatore non deve passare al plenum di ripresa e alla griglia.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>C.1</t>
+          <t>B.12</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_liquid/tubo-rame-liquido</t>
+          <t>Isolamento elastomerico adesivo per raccordi e plenum</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>T07 12 m</t>
+          <t>PLZ-01: 1</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 «Refrigerante» (isolamento dal manuale di installazione Daikin FTXM60-71A, citato in RAPPORTO.md §10)</t>
+          <t>regola Nove C per la posa del plenum di zona</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>La linea del liquido, a metro, con la lunghezza da quotare.</t>
+          <t>I raccordi rigidi fra macchina, plenum e curve fanno condensa se non si isolano.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>C.2</t>
+          <t>B.13</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_liquid/manicotti-a-brasare-liquido</t>
+          <t>Plenum di ripresa coibentato con filtro ispezionabile, bocca 1000×250, sulla bocca di aspirazione dell'unità interna</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>2 per sezione</t>
+          <t>RA-01: 1</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py («Manicotto a brasare 1/4" e 1/2"», n 4 per le due linee)</t>
+          <t>regola Nove C per la ripresa dell'aria</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>La linea si posa in un pezzo solo; due manicotti di riserva per linea coprono una giunta imprevista.</t>
+          <t>Un filtro solo, ispezionabile: due filtri in serie (plenum e griglia) raddoppiano la perdita.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>C.3</t>
+          <t>B.14</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_gas/tubo-rame-gas</t>
+          <t>Plenum porta-bocchetta coibentato per bocchetta 400×200, attacco Ø200 laterale o dall'alto</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>T08 12 m</t>
+          <t>5 pezzi × 1 = 5 (B1, B2, B3, B4, B5)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 «Refrigerante» (manuale di installazione Daikin FTXM60-71A, citato in RAPPORTO.md §10)</t>
+          <t>regola Nove C per le bocchette di mandata</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>La linea del gas, a metro, con la lunghezza da quotare.</t>
+          <t>Il plenum si ordina sulla misura della bocchetta: è un dato del progettista sul pezzo (`dimensione`).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>C.4</t>
+          <t>C.1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_gas/manicotti-a-brasare-gas</t>
+          <t>Tubo rame ricotto pre-isolato Ø6,35 (1/4"), isolamento ≥ 10 mm, resistente a 120 °C</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>2 per sezione</t>
+          <t>T07 12 m</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py («Manicotto a brasare 1/4" e 1/2"», n 4 per le due linee)</t>
+          <t>manuale di installazione del costruttore della macchina (isolamento delle linee)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Come per il liquido: due di riserva per linea.</t>
+          <t>La linea del liquido, a metro, con la lunghezza da quotare.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>C.5</t>
+          <t>C.2</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_gas/nastro-e-manicotti-isolanti</t>
+          <t>Manicotto a brasare Ø6,35 (1/4") (riserva, posa in tratta unica)</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>1 tratto × 1 = 1</t>
+          <t>2 per sezione</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce C.4</t>
+          <t>regola Nove C per le linee frigorifere</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Una coppia di linee (liquido e gas) per kit: si conta sulla linea del gas, che ogni coppia ha una volta sola.</t>
+          <t>La linea si posa in un pezzo solo; due manicotti di riserva per linea coprono una giunta imprevista.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>C.6</t>
+          <t>C.3</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_gas/collari-linee-frigo</t>
+          <t>Tubo rame ricotto pre-isolato Ø12,7 (1/2"), isolamento ≥ 13 mm, resistente a 120 °C</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>T08 10 (L / 1,2 m per eccesso per tratto)</t>
+          <t>T08 12 m</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce C.7 (10 collari per 12 m)</t>
+          <t>manuale di installazione del costruttore della macchina (isolamento delle linee)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>La coppia pre-isolata si sostiene ogni 1,2 m, come il flessibile: un collare per passo, sulla linea del gas che porta la coppia.</t>
+          <t>La linea del gas, a metro, con la lunghezza da quotare.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>C.7</t>
+          <t>C.4</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_gas/carica-aggiuntiva</t>
+          <t>Manicotto a brasare Ø12,7 (1/2") (riserva, posa in tratta unica)</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>mancano i dati di macchina</t>
+          <t>2 per sezione</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (precarica fino a 10 m, oltre 20 g/m: scheda Daikin RXM-A, citata in RAPPORTO.md §10); REVISIONE-INDIPENDENTE.md rilievo 18 (riserva di 0,2 kg)</t>
+          <t>regola Nove C per le linee frigorifere</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Oltre la lunghezza precaricata dall'unità esterna serve refrigerante a grammi per metro; anche dentro, una riserva minima per il rabbocco dopo la prova. I dati (`precarica_fino_a_m`, `carica_aggiuntiva_g_m`, `refrigerante`) li dà il progettista sull'unità esterna: se mancano, la voce è DA DEFINIRE.</t>
+          <t>Come per il liquido: due di riserva per linea.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>C.8</t>
+          <t>C.5</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>corredo/split-outdoor-unit/canalina-esterna</t>
+          <t>Nastro di finitura e manicotti isolanti per le giunzioni a cartella</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>UE-01: 4</t>
+          <t>1 tratto × 1 = 1</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce C.5; REVISIONE-INDIPENDENTE.md rilievo 18</t>
+          <t>regola Nove C per le linee frigorifere</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Il tratto a vista sulla facciata, dal foro all'unità esterna.</t>
+          <t>Una coppia di linee (liquido e gas) per kit: si conta sulla linea del gas, che ogni coppia ha una volta sola.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>C.9</t>
+          <t>C.6</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>corredo/split-outdoor-unit/accessori-canalina</t>
+          <t>Collare di sostegno linee frigorifere in controsoffitto</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>UE-01: 1</t>
+          <t>T08 10 (L / 1,2 m per eccesso per tratto)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce C.6; REVISIONE-INDIPENDENTE.md rilievo 18 («canalina con accessori a numero»)</t>
+          <t>regola Nove C per le linee frigorifere</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Una canalina senza curve e terminali non si chiude.</t>
+          <t>La coppia pre-isolata si sostiene ogni 1,2 m, come il flessibile: un collare per passo, sulla linea del gas che porta la coppia.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>C.10</t>
+          <t>C.7</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>corredo/split-outdoor-unit/staffe-unita-esterna</t>
+          <t>Refrigerante R32, riserva per carica aggiuntiva</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>UE-01: 1</t>
+          <t>mancano i dati di macchina</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce C.8 (portata ≥ 100 kg per 49 kg)</t>
+          <t>scheda tecnica dell'unità esterna (precarica e carica aggiuntiva)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Nota: o piedini a terra, secondo la posizione.</t>
+          <t>Oltre la lunghezza precaricata dall'unità esterna serve refrigerante a grammi per metro; anche dentro, una riserva minima per il rabbocco dopo la prova. I dati (`precarica_fino_a_m`, `carica_aggiuntiva_g_m`, `refrigerante`) li dà il progettista sull'unità esterna: se mancano, la voce è DA DEFINIRE.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>C.11</t>
+          <t>C.8</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>corredo/split-outdoor-unit/scarico-condensa-unita-esterna</t>
+          <t>Canalina coprilinee esterna 80×60</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -6015,1303 +6083,1303 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce C.9; REVISIONE-INDIPENDENTE.md rilievo 18</t>
+          <t>regola Nove C per la posa dell'unità esterna</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>In riscaldamento l'unità esterna sbrina e scarica acqua: senza scarico gela sul marciapiede.</t>
+          <t>Il tratto a vista sulla facciata, dal foro all'unità esterna.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>C.9</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/tubo-pvc</t>
+          <t>Accessori canalina: curva 2, terminale a muro 1, giunto 2</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>T09 10 m</t>
+          <t>UE-01: 1</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 «Condensa»</t>
+          <t>regola Nove C per la posa dell'unità esterna</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Lo scarico della condensa, a metro, con la lunghezza da quotare.</t>
+          <t>Una canalina senza curve e terminali non si chiude.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>D.2</t>
+          <t>C.10</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/curve-condensa</t>
+          <t>Staffe a parete per unità esterna, portata almeno doppia del peso della macchina, con antivibranti</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>T09 6 (L / 2 m per eccesso +1 per tratto)</t>
+          <t>UE-01: 1</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.3 (6 curve su 10 m); il passo è della sessione di sviluppo, che riproduce il kit: da confermare</t>
+          <t>regola Nove C per la posa dell'unità esterna</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Il percorso in controsoffitto con la pendenza cambia spesso direzione: una curva ogni 2 m più quella della discesa.</t>
+          <t>Nota: o piedini a terra, secondo la posizione.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>D.3</t>
+          <t>C.11</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/manicotti-condensa</t>
+          <t>Scarico condensa dell'unità esterna (funziona anche in caldo): raccordo e tubo Ø16 fino a pluviale o pozzetto</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>T09 3 (L / 3 m per eccesso -1 per tratto)</t>
+          <t>UE-01: 4</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.4 (3 manicotti su 10 m); barre da 3 m, assunzione della sessione di sviluppo: da confermare</t>
+          <t>regola Nove C per la posa dell'unità esterna</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Una giunzione fra due barre.</t>
+          <t>In riscaldamento l'unità esterna sbrina e scarica acqua: senza scarico gela sul marciapiede.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/collari-condensa</t>
+          <t>Tubo PVC rigido Ø32</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>T09 10 (L / 1 m per eccesso per tratto)</t>
+          <t>T09 10 m</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.7 (10 collari su 10 m)</t>
+          <t>regola Nove C per lo scarico della condensa</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Il tubo piccolo in pendenza si sostiene fitto, o la pendenza si perde fra due collari.</t>
+          <t>Lo scarico della condensa, a metro, con la lunghezza da quotare.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>D.5</t>
+          <t>D.2</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/isolamento-anticondensa</t>
+          <t>Curva 87°-90° Ø32</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>T09 10 m</t>
+          <t>T09 6 (L / 2 m per eccesso +1 per tratto)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.8 (5 m, il solo tratto in controsoffitto, scritto a mano sul caso)</t>
+          <t>stima Nove C (una curva ogni 2 m)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>La condensa fredda in controsoffitto gocciola fuori dal tubo. Su tutta la lunghezza, in dubbio per eccesso: la parte in controsoffitto la sa solo la pianta.</t>
+          <t>Il percorso in controsoffitto con la pendenza cambia spesso direzione: una curva ogni 2 m più quella della discesa.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>D.6</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/collante-pvc</t>
+          <t>Manicotto Ø32</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>1 per fluido</t>
+          <t>T09 3 (L / 3 m per eccesso -1 per tratto)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.9</t>
+          <t>stima Nove C (barre da 3 m)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Una confezione per lo scarico.</t>
+          <t>Una giunzione fra due barre.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>D.7</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>corredo/ducted-indoor-unit/raccordo-condensa-unita-interna</t>
+          <t>Collare per tubo condensa</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>UI-01: 1</t>
+          <t>T09 10 (L / 1 m per eccesso per tratto)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.2; REVISIONE-INDIPENDENTE.md rilievo 6</t>
+          <t>regola Nove C per lo scarico della condensa</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>L'attacco della macchina (VP20 nel caso) non è il diametro del PVC: senza il raccordo lo scarico non si collega. L'attacco è un dato di macchina del progettista (`attacco_condensa`).</t>
+          <t>Il tubo piccolo in pendenza si sostiene fitto, o la pendenza si perde fra due collari.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>D.8</t>
+          <t>D.5</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>corredo/condensate-trap/sifone</t>
+          <t>Isolamento anticondensa 9 mm per il tubo della condensa</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>SIF-01: 1</t>
+          <t>T09 10 m</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.5</t>
+          <t>regola Nove C per lo scarico della condensa</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Senza sifone l'odore dello scarico risale nella macchina.</t>
+          <t>La condensa fredda in controsoffitto gocciola fuori dal tubo. Su tutta la lunghezza, in dubbio per eccesso: la parte in controsoffitto la sa solo la pianta.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>D.9</t>
+          <t>D.6</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>corredo/condensate-outlet/innesto-sullo-scarico</t>
+          <t>Collante e pulitore PVC</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>scarico: 1</t>
+          <t>1 per fluido</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce D.6</t>
+          <t>regola Nove C per lo scarico della condensa</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>L'allaccio della condensa a uno scarico esistente.</t>
+          <t>Una confezione per lo scarico.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>D.7</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>fluidi/power_supply/cavo-di-alimentazione</t>
+          <t>Raccordo di adattamento dall'attacco condensa dell'unità interna (VP20 (Øe 26)) al tubo di scarico, con fascetta</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>T10 20 m</t>
+          <t>UI-01: 1</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 «Elettrico e bus» (linea dedicata in FG16OR16); la sezione del cavo è un dato del progettista (`sezione` del tratto)</t>
+          <t>scheda tecnica dell'unità interna (attacco della condensa)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Una riga per sezione di cavo, a metro, con la lunghezza da quotare.</t>
+          <t>L'attacco della macchina (VP20 nel caso) non è il diametro del PVC: senza il raccordo lo scarico non si collega. L'attacco è un dato di macchina del progettista (`attacco_condensa`).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>E.2</t>
+          <t>D.8</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>fluidi/power_supply/cavo-di-alimentazione</t>
+          <t>Sifone ispezionabile per condensa</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>T11 15 m</t>
+          <t>SIF-01: 1</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 «Elettrico e bus» (linea dedicata in FG16OR16); la sezione del cavo è un dato del progettista (`sezione` del tratto)</t>
+          <t>regola Nove C per lo scarico della condensa</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Una riga per sezione di cavo, a metro, con la lunghezza da quotare.</t>
+          <t>Senza sifone l'odore dello scarico risale nella macchina.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>E.3</t>
+          <t>D.9</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>fluidi/power_supply/protezione-della-linea</t>
+          <t>Innesto sullo scarico esistente (braga 45° o presa sul sifone di un apparecchio)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>una per tratto: T10</t>
+          <t>AL-01: 1</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7; REVISIONE-INDIPENDENTE.md rilievi 7 e 12 (la protezione della centrale a sé, verificare la targa della macchina)</t>
+          <t>regola Nove C per lo scarico della condensa</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Ogni linea dedicata ha la sua protezione nel quadro. La taglia dipende dalla targa della macchina: è un dato del progettista (`protezione` del tratto); se manca, la voce è DA DEFINIRE.</t>
+          <t>L'allaccio della condensa a uno scarico esistente.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>fluidi/power_supply/protezione-della-linea</t>
+          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>una per tratto: T11</t>
+          <t>T10 20 m</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7; REVISIONE-INDIPENDENTE.md rilievi 7 e 12 (la protezione della centrale a sé, verificare la targa della macchina)</t>
+          <t>regola Nove C per le linee elettriche dedicate</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Ogni linea dedicata ha la sua protezione nel quadro. La taglia dipende dalla targa della macchina: è un dato del progettista (`protezione` del tratto); se manca, la voce è DA DEFINIRE.</t>
+          <t>Una riga per sezione di cavo, a metro, con la lunghezza da quotare.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>E.5</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>fluidi/power_supply/scatola-di-derivazione</t>
+          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>2 tratti × 1 = 2</t>
+          <t>T11 15 m</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce E.12 (2 scatole per 2 linee)</t>
+          <t>regola Nove C per le linee elettriche dedicate</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Una scatola per linea, all'uscita dal controsoffitto o all'ingresso nella macchina.</t>
+          <t>Una riga per sezione di cavo, a metro, con la lunghezza da quotare.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>E.6</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>fluidi/power_supply/corrugato-di-potenza</t>
+          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>T10 20 + T11 15 = 35 m × 1, per eccesso a 10 m = 40 m</t>
+          <t>una per tratto: T10</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce E.10 (40 m per 35 m di linee); l'arrotondamento a 10 m è della sessione di sviluppo, che riproduce il kit: da confermare</t>
+          <t>targa della macchina (dato del progettista)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Ogni metro di cavo di potenza corre in corrugato; si compra a decine di metri.</t>
+          <t>Ogni linea dedicata ha la sua protezione nel quadro. La taglia dipende dalla targa della macchina: è un dato del progettista (`protezione` del tratto); se manca, la voce è DA DEFINIRE.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>E.7</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>fluidi/interconnection/cavo-di-collegamento</t>
+          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>T12 13 m</t>
+          <t>una per tratto: T11</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (cavo a 4 conduttori ≥ 1,5 mm² a doppio isolamento, dal manuale di installazione Daikin FTXM60-71A citato in RAPPORTO.md §10)</t>
+          <t>targa della macchina (dato del progettista)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Corre con le linee frigorifere, nella loro canalina: niente corrugato (kit, voci E.10 ed E.11).</t>
+          <t>Ogni linea dedicata ha la sua protezione nel quadro. La taglia dipende dalla targa della macchina: è un dato del progettista (`protezione` del tratto); se manca, la voce è DA DEFINIRE.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>E.8</t>
+          <t>E.5</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>fluidi/control_bus/cavo-di-bus</t>
+          <t>Scatola di derivazione IP55</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>T13 5 + T14 5,5 = 10,5 m</t>
+          <t>2 tratti × 1 = 2</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (bus a stella dalla centrale; P1-P2 per gateway e comando a filo)</t>
+          <t>regola Nove C per le linee elettriche dedicate</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Una riga per tipo di cavo (la `sezione` del tratto: «2×0,75 (P1-P2)», «bus Airzone, schermato»), a metro.</t>
+          <t>Una scatola per linea, all'uscita dal controsoffitto o all'ingresso nella macchina.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>E.9</t>
+          <t>E.6</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>fluidi/control_bus/cavo-di-bus</t>
+          <t>Tubo corrugato Ø25 per le linee di alimentazione</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>T15 9 + T16 7 + T17 7,5 + T18 5,5 = 29 m</t>
+          <t>T10 20 + T11 15 = 35 m × 1, per eccesso a 10 m = 40 m</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (bus a stella dalla centrale; P1-P2 per gateway e comando a filo)</t>
+          <t>stima Nove C (corrugato a decine di metri)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Una riga per tipo di cavo (la `sezione` del tratto: «2×0,75 (P1-P2)», «bus Airzone, schermato»), a metro.</t>
+          <t>Ogni metro di cavo di potenza corre in corrugato; si compra a decine di metri.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>E.10</t>
+          <t>E.7</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>fluidi/control_bus/corrugato-di-bus</t>
+          <t>Cavo di collegamento 4G1,5 a doppio isolamento, Collegamento UI-UE</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>T13 5 + T14 5,5 + T15 9 + T16 7 + T17 7,5 + T18 5,5 = 39,5 m × 1, per eccesso a 10 m = 40 m</t>
+          <t>T12 13 m</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce E.11 (40 m per 37,5 m di bus); l'arrotondamento a 10 m è della sessione di sviluppo: da confermare</t>
+          <t>manuale di installazione del costruttore della macchina</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Il bus corre separato dalle linee di potenza, nel suo corrugato.</t>
+          <t>Corre con le linee frigorifere, nella loro canalina: niente corrugato (kit, voci E.10 ed E.11).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>E.11</t>
+          <t>E.8</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>corredo/electrical-panel/aggiornamento-schema-quadro</t>
+          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>QE-01: 1</t>
+          <t>T13 5 + T14 5,5 = 10,5 m</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce E.6; REVISIONE-INDIPENDENTE.md rilievo 12</t>
+          <t>regola Nove C per i bus e le linee di comando</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Una protezione nuova nel quadro cambia lo schema, che va aggiornato e allegato alla dichiarazione di conformità.</t>
+          <t>Una riga per tipo di cavo (la `sezione` del tratto: «2×0,75 (P1-P2)», «bus Airzone, schermato»), a metro.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>E.12</t>
+          <t>E.9</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>corredo/isolator-switch/sezionatore</t>
+          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>SZ-01: 1</t>
+          <t>T15 9 + T16 7 + T17 7,5 + T18 5,5 = 29 m</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: RAPPORTO.md §7 (apertura dei contatti ≥ 3 mm dal manuale di installazione Daikin FTXM60-71A, citato in RAPPORTO.md §10)</t>
+          <t>regola Nove C per i bus e le linee di comando</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Chi fa manutenzione all'unità esterna la stacca lì accanto.</t>
+          <t>Una riga per tipo di cavo (la `sezione` del tratto: «2×0,75 (P1-P2)», «bus Airzone, schermato»), a metro.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>E.13</t>
+          <t>E.10</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>corredo/room-thermostat/scatola-503 + corredo/wired-remote/scatola-503</t>
+          <t>Tubo corrugato Ø20 per bus e linee di comando</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>5 pezzi × 1 = 5 (TZ-01, TZ-02, TZ-03, TZ-04, CF-01)</t>
+          <t>T13 5 + T14 5,5 + T15 9 + T16 7 + T17 7,5 + T18 5,5 = 39,5 m × 1, per eccesso a 10 m = 40 m</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce E.13</t>
+          <t>stima Nove C (corrugato a decine di metri)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Il termostato si monta su una scatola da incasso.</t>
+          <t>Il bus corre separato dalle linee di potenza, nel suo corrugato.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>E.11</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/foratura-per-flessibile</t>
+          <t>Aggiornamento dello schema del quadro elettrico</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>T01 2 + T02 1 + T03 2 + T04 1 + T05 1 = 7</t>
+          <t>QE-01: 1</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.3; REVISIONE-INDIPENDENTE.md rilievi 1 e 11 (le aperture sono dell'installatore)</t>
+          <t>regola Nove C per le linee elettriche dedicate</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>La macchina sta in un disimpegno e le bocchette nelle stanze: ogni ramo passa almeno una parete. Il progettista scrive sul tratto quante ne passa (`attraversamenti`); se non lo scrive, se ne conta una.</t>
+          <t>Una protezione nuova nel quadro cambia lo schema, che va aggiornato e allegato alla dichiarazione di conformità.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>E.12</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>fluidi/refrigerant_gas/foratura-linee-frigo</t>
+          <t>Sezionatore onnipolare di prossimità IP55, apertura contatti ≥ 3 mm</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>T08 2</t>
+          <t>SZ-01: 1</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.2; REVISIONE-INDIPENDENTE.md rilievo 11</t>
+          <t>manuale di installazione del costruttore della macchina (apertura dei contatti)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Le aperture sono dell'installatore (le chiusure del committente). Il progettista scrive sul tratto quante pareti interne passa; se non lo scrive, se ne conta una. Il foro nella parete esterna è nel corredo dell'unità esterna.</t>
+          <t>Chi fa manutenzione all'unità esterna la stacca lì accanto.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>E.13</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>fluidi/condensate/foratura-condensa</t>
+          <t>Scatola 503 per termostati e comandi a parete</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>T09 1</t>
+          <t>5 pezzi × 1 = 5 (TZ-01, TZ-02, TZ-03, TZ-04, CF-01)</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.4</t>
+          <t>regola Nove C per gli apparecchi a parete</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Lo scarico sta in un altro locale (il bagno più vicino): il progettista scrive le pareti passate; se non lo scrive, se ne conta una.</t>
+          <t>Il termostato si monta su una scatola da incasso.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>corredo/split-outdoor-unit/carotaggio-parete-esterna</t>
+          <t>Foratura di tramezza Ø250 (o vano 450×250) per flessibili e plenum di bocchetta</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>UE-01: 1</t>
+          <t>T01 2 + T02 1 + T03 2 + T04 1 + T05 1 = 7</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.1</t>
+          <t>regola Nove C per le assistenze murarie</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Le linee frigorifere e il cavo di collegamento escono dall'involucro una volta.</t>
+          <t>La macchina sta in un disimpegno e le bocchette nelle stanze: ogni ramo passa almeno una parete. Il progettista scrive sul tratto quante ne passa (`attraversamenti`); se non lo scrive, se ne conta una.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>F.5</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>corredo/condensate-outlet/traccia-condensa</t>
+          <t>Foratura di parete interna Ø80 per linee frigorifere e cavi</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>scarico: 3</t>
+          <t>T08 2</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.5 (3 m nel bagno)</t>
+          <t>regola Nove C per le assistenze murarie</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>La discesa dal controsoffitto allo scarico è in traccia.</t>
+          <t>Le aperture sono dell'installatore (le chiusure del committente). Il progettista scrive sul tratto quante pareti interne passa; se non lo scrive, se ne conta una. Il foro nella parete esterna è nel corredo dell'unità esterna.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>corredo/electrical-panel/tracce-dal-quadro</t>
+          <t>Foratura per lo scarico della condensa</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>QE-01: 5</t>
+          <t>T09 1</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.6 (5 m per due linee); 2,5 m di discesa per linea è della sessione di sviluppo, che riproduce il kit: da confermare</t>
+          <t>regola Nove C per le assistenze murarie</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Ogni linea dedicata scende dal controsoffitto al quadro in traccia.</t>
+          <t>Lo scarico sta in un altro locale (il bagno più vicino): il progettista scrive le pareti passate; se non lo scrive, se ne conta una.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>corredo/room-thermostat/traccia-per-apparecchio-a-parete + corredo/wired-remote/traccia-per-apparecchio-a-parete</t>
+          <t>Carotaggio parete esterna Ø80 con guaina passante e sigillatura</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>5 pezzi × 1 = 5 (TZ-01, TZ-02, TZ-03, TZ-04, CF-01)</t>
+          <t>UE-01: 1</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce F.7</t>
+          <t>regola Nove C per le assistenze murarie</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Il cavo scende dal controsoffitto alla scatola in traccia.</t>
+          <t>Le linee frigorifere e il cavo di collegamento escono dall'involucro una volta.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Z.1</t>
+          <t>F.5</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>fluidi/supply_air/velette-per-le-bocchette</t>
+          <t>Traccia per la condensa fino allo scarico</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>1 per fluido</t>
+          <t>AL-01: 3</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.3; REVISIONE-INDIPENDENTE.md rilievo 5</t>
+          <t>stima Nove C (3 m di traccia fino allo scarico)</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Il plenum porta-bocchetta con l'attacco del flessibile ha bisogno di 30 cm: se manca la veletta, la bocchetta non si monta.</t>
+          <t>La discesa dal controsoffitto allo scarico è in traccia.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Z.2</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>corredo/ducted-indoor-unit/controsoffitto-zona-macchina</t>
+          <t>Tracce per le linee dal quadro al controsoffitto</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>UI-01: 1</t>
+          <t>QE-01: 5</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.1 (altezza della FBA60A9 245 mm più sospensioni e pendenza della condensa)</t>
+          <t>stima Nove C (2,5 m di traccia per linea)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Senza l'altezza libera la macchina non entra: è un'opera del committente da coordinare prima della gara.</t>
+          <t>Ogni linea dedicata scende dal controsoffitto al quadro in traccia.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Z.3</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>corredo/ducted-indoor-unit/botola-di-ispezione + corredo/zoning-plenum-5/botola-di-ispezione</t>
+          <t>Traccia per termostati e comandi a parete</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>2 pezzi × 1 = 2 (UI-01, PLZ-01)</t>
+          <t>5 pezzi × 1 = 5 (TZ-01, TZ-02, TZ-03, TZ-04, CF-01)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.2 | kit AA-01: lavoro/dimensionamento.py, voce Z.2 («sotto UI … e sotto plenum e centrale», n 2)</t>
+          <t>regola Nove C per gli apparecchi a parete</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Filtro, pompa della condensa e scheda si raggiungono da sotto.</t>
+          <t>Il cavo scende dal controsoffitto alla scatola in traccia.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Z.4</t>
+          <t>Z.1</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>corredo/return-air-terminal/griglia-di-ripresa</t>
+          <t>Velette o controsoffitti per le bocchette, altezza utile ≥ 30 cm</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>RA-01: 1</t>
+          <t>1 per fluido</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.5</t>
+          <t>regola Nove C per le bocchette in controsoffitto</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Apribile: il filtro sta dietro.</t>
+          <t>Il plenum porta-bocchetta con l'attacco del flessibile ha bisogno di 30 cm: se manca la veletta, la bocchetta non si monta.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Z.5</t>
+          <t>Z.2</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>corredo/air-supply-terminal/bocchetta-di-mandata</t>
+          <t>Controsoffitto in zona unità interna e plenum: altezza libera ≥ 35 cm sotto il solaio</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>5 pezzi × 1 = 5 (B1, B2, B3, B4, B5)</t>
+          <t>UI-01: 1</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.4 (bocchette del committente nell'offerta del caso)</t>
+          <t>regola Nove C per la posa dell'unità interna canalizzata (ingombro della macchina)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Chi fornisce le bocchette lo dice l'offerta: nel kit sono del committente. Se le fornisce l'installatore, si cambia la fornitura di questa voce, qui: la distinta non legge la fornitura dal grafo.</t>
+          <t>Senza l'altezza libera la macchina non entra: è un'opera del committente da coordinare prima della gara.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Z.6</t>
+          <t>Z.3</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>corredo/air-supply-terminal/griglia-di-transito</t>
+          <t>Botola di ispezione ≥ 600×600 sotto la macchina (filtro, pompa, scheda)</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>5 pezzi × 1 = 5 (B1, B2, B3, B4, B5)</t>
+          <t>2 pezzi × 1 = 2 (UI-01, PLZ-01)</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.6; REVISIONE-INDIPENDENTE.md rilievo 28</t>
+          <t>regola Nove C per la posa dell'unità interna canalizzata; regola Nove C per la posa del plenum di zona</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Senza un passaggio, l'aria immessa non torna alla ripresa: la portata cala e cresce il rumore. L'area efficace minima per bocchetta è nella verifica dell'aria.</t>
+          <t>Filtro, pompa della condensa e scheda si raggiungono da sotto.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Z.7</t>
+          <t>Z.4</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>attivita/chiusure-e-ripristini</t>
+          <t>Griglia di ripresa 1000×250 senza filtro, apribile per accedere al filtro</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>sempre</t>
+          <t>RA-01: 1</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, voce Z.7; REVISIONE-INDIPENDENTE.md rilievo 11 (l'offerta esclude chiusure e ripristini)</t>
+          <t>regola Nove C per la ripresa dell'aria</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Le aperture sono dell'installatore, chiusure e ripristini del committente: va scritto, o diventa una lite.</t>
+          <t>Apribile: il filtro sta dietro.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>Z.5</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>attivita/posa-unita-interna</t>
+          <t>Bocchetta di mandata 400×200 a doppio filare con serranda</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: ducted-indoor-unit</t>
+          <t>5 pezzi × 1 = 5 (B1, B2, B3, B4, B5)</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[0]</t>
+          <t>regola Nove C per le bocchette di mandata</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>La posa delle macchine fornite da Nove C è manodopera dell'installatore, a corpo.</t>
+          <t>Chi fornisce le bocchette è una scelta dell'offerta (`distinta.json`, fornitura «bocchette_e_griglie»): nelle offerte Nove C sono del Committente.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>Z.6</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>attivita/posa-unita-esterna</t>
+          <t>Griglia di transito o luce sotto porta per il ritorno dell'aria dal locale servito</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: split-outdoor-unit</t>
+          <t>4: 4 locali serviti (Camera 13 m², Camera 15 m², Camera 16 m², Soggiorno-cucina); il locale e' letto dall'etichetta della bocchetta</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[1]</t>
+          <t>regola Nove C per il ritorno dell'aria</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Come sopra.</t>
+          <t>Senza un passaggio, l'aria immessa non torna alla ripresa: la portata cala e cresce il rumore. Una per locale servito, non per bocchetta: due bocchette nello stesso locale ne vogliono una sola, e un locale con un varco aperto verso la ripresa nessuna. Il locale è il dato `locale` della bocchetta (o, se manca, la sua etichetta senza le parentesi); il varco è `varco` sulla bocchetta. L'area efficace minima per locale è nella verifica dell'aria.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>Z.7</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>attivita/linee-frigorifere-e-prove</t>
+          <t>Chiusura e ripristino di fori, tracce e passaggi</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: refrigerant_liquid, refrigerant_gas</t>
+          <t>sempre</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[2]; REVISIONE-INDIPENDENTE.md rilievo 14 (prove fra i due accessi)</t>
+          <t>regola Nove C per le offerte a corpo (aperture all'installatore, chiusure a chi fa le opere edili)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>La tenuta si prova prima di chiudere il controsoffitto: dopo, una perdita costa la demolizione. Il manometro fino al secondo accesso dice se il circuito ha tenuto nel frattempo.</t>
+          <t>Le aperture sono dell'installatore, chiusure e ripristini del committente: va scritto, o diventa una lite.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>attivita/distribuzione-aria</t>
+          <t>Posa dell'unità interna in controsoffitto su sospensioni antivibranti, con plenum di zona e plenum di ripresa.</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: supply_air</t>
+          <t>nell'impianto: Unità interna canalizzata ad espansione diretta</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[3]</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Le bocche aperte in cantiere si riempiono di polvere, che poi esce dalle bocchette.</t>
+          <t>La posa delle macchine fornite da Nove C è manodopera dell'installatore, a corpo.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>attivita/scarico-condensa-e-prova</t>
+          <t>Posa dell'unità esterna su staffe con antivibranti; canalina esterna e scarico condensa dell'unità esterna.</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: condensate</t>
+          <t>nell'impianto: Unità esterna split a pompa di calore</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[4]; REVISIONE-INDIPENDENTE.md rilievo 14</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Come la tenuta: la condensa si prova a controsoffitto aperto.</t>
+          <t>Come sopra.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>attivita/linee-elettriche-e-comandi</t>
+          <t>Linee frigorifere: posa e cartelle; prova di tenuta in azoto prima della chiusura del controsoffitto, circuito lasciato in pressione con manometro fino al secondo accesso, con verbale; vuoto, apertura rubinetti, eventuale carica, registrazione F-Gas.</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: power_supply, interconnection, control_bus</t>
+          <t>nell'impianto: fluido frigorigeno in fase liquida, fluido frigorigeno in fase gassosa</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[5]</t>
+          <t>regola Nove C per le prove delle linee frigorifere; regolamento F-Gas</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>La posa e i collegamenti del materiale della sezione E.</t>
+          <t>La tenuta si prova prima di chiudere il controsoffitto: dopo, una perdita costa la demolizione. Il manometro fino al secondo accesso dice se il circuito ha tenuto nel frattempo.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>attivita/messa-in-servizio</t>
+          <t>Distribuzione aria: 5 rami flessibili con plenum porta-bocchetta, sostegni e sigillature; bocche protette fino alla posa delle bocchette.</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: ducted-indoor-unit, split-outdoor-unit</t>
+          <t>nell'impianto: aria di mandata</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[6]; REVISIONE-INDIPENDENTE.md rilievi 8 e 16 (collaudo con portate misurate e verbale)</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>La prevalenza si regola sulla rete vera, e le portate misurate sono la prova che l'impianto fa quello che promette.</t>
+          <t>Le bocche aperte in cantiere si riempiono di polvere, che poi esce dalle bocchette.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>G.8</t>
+          <t>G.5</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>attivita/dico-elettrico</t>
+          <t>Scarico condensa con sifone e allaccio allo scarico; prova di scarico e della pompa prima della chiusura del controsoffitto.</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: power_supply</t>
+          <t>nell'impianto: condensa</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[7]; REVISIONE-INDIPENDENTE.md rilievo 16 (due DiCo)</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Le linee dedicate sono un impianto elettrico: la sua dichiarazione è distinta da quella della climatizzazione.</t>
+          <t>Come la tenuta: la condensa si prova a controsoffitto aperto.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>G.9</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>attivita/dico-climatizzazione</t>
+          <t>Linee elettriche dedicate dal quadro, collegamento fra le unità, linee di comando e bus; posa di termostati e comandi a parete.</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: refrigerant_liquid, refrigerant_gas, supply_air</t>
+          <t>nell'impianto: alimentazione elettrica, collegamento elettrico fra le unita', bus di comando</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[7]; REVISIONE-INDIPENDENTE.md rilievo 16</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Come sopra.</t>
+          <t>La posa e i collegamenti del materiale della sezione E.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>G.10</t>
+          <t>G.7</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>attivita/cantiere</t>
+          <t>Messa in servizio con Nove C, al secondo accesso: regolazione della prevalenza dell'unità interna e misura delle portate per zona, configurazione della zonizzazione e dei comandi, app; collaudo con verbale.</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>sempre</t>
+          <t>nell'impianto: Unità interna canalizzata ad espansione diretta, Unità esterna split a pompa di calore</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[8]; REVISIONE-INDIPENDENTE.md rilievo 13</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Mancavano nella prima stesura del kit: sono costi veri dell'installatore, e se non sono a corpo diventano extra.</t>
+          <t>La prevalenza si regola sulla rete vera, e le portate misurate sono la prova che l'impianto fa quello che promette.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>G.11</t>
+          <t>G.8</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>attivita/custodia-e-protezioni</t>
+          <t>Dichiarazione di conformità D.M. 37/2008, art. 1 lettera a) (impianti elettrici), con lo schema del quadro aggiornato e gli allegati.</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: split-outdoor-unit, ducted-indoor-unit, zoning-plenum-5</t>
+          <t>nell'impianto: alimentazione elettrica</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[9]; REVISIONE-INDIPENDENTE.md rilievo 13</t>
+          <t>D.M. 37/2008</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Le macchine di Nove C stanno in cantiere settimane prima della posa.</t>
+          <t>Le linee dedicate sono un impianto elettrico: la sua dichiarazione è distinta da quella della climatizzazione.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>G.12</t>
+          <t>G.9</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>attivita/pulizia-e-smaltimenti</t>
+          <t>Dichiarazione di conformità D.M. 37/2008, art. 1 lettera c) (impianti di climatizzazione), con allegati; documenti per libretto di impianto, catasto regionale e F-Gas.</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>sempre</t>
+          <t>nell'impianto: fluido frigorigeno in fase liquida, fluido frigorigeno in fase gassosa, aria di mandata</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, ATTIVITA[10]; REVISIONE-INDIPENDENTE.md rilievo 13</t>
+          <t>D.M. 37/2008</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -7323,133 +7391,214 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>V.1</t>
+          <t>G.10</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>attivita/variante-linea-frigorifera</t>
+          <t>Cantiere: POS e oneri della sicurezza (presenza dell'impresa del Committente), trabattello e mezzi di sollevamento.</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: refrigerant_liquid, refrigerant_gas; solo prezzo unitario</t>
+          <t>sempre</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, VARIANTI V.1; REVISIONE-INDIPENDENTE.md rilievi 10 e 20</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Se l'unità esterna va su un'altra facciata, il metro in più ha già un prezzo, fissato prima.</t>
+          <t>Mancavano nella prima stesura del kit: sono costi veri dell'installatore, e se non sono a corpo diventano extra.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>V.2</t>
+          <t>G.11</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>attivita/variante-flessibile</t>
+          <t>Trasporto, ricevimento e custodia delle apparecchiature fornite da Nove C fino al collaudo; protezioni delle macchine e delle bocche durante le opere edili.</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: supply_air; solo prezzo unitario</t>
+          <t>nell'impianto: Unità esterna split a pompa di calore, Unità interna canalizzata ad espansione diretta, Plenum motorizzato di zona a cinque serrande</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, VARIANTI V.2</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Come sopra.</t>
+          <t>Le macchine di Nove C stanno in cantiere settimane prima della posa.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>V.3</t>
+          <t>G.12</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>attivita/variante-cavo</t>
+          <t>Pulizia finale e smaltimento di imballi e residui di lavorazione.</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>nel grafo: power_supply; solo prezzo unitario</t>
+          <t>sempre</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, VARIANTI V.3</t>
+          <t>regola Nove C per le offerte a corpo</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>La posizione del quadro si conferma in sopralluogo.</t>
+          <t>Come sopra.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>V.4</t>
+          <t>V.1</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>attivita/variante-accesso</t>
+          <t>Linea frigorifera completa oltre la quantità di computo (coppia pre-isolata, cavo di collegamento, canalina, refrigerante)</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>sempre; solo prezzo unitario</t>
+          <t>nell'impianto: fluido frigorigeno in fase liquida, fluido frigorigeno in fase gassosa; solo prezzo unitario</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, VARIANTI V.4; REVISIONE-INDIPENDENTE.md rilievo 14 (terzo accesso)</t>
+          <t>regola Nove C per le varianti a prezzo unitario</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Il prezzo a corpo vale per due accessi: posa con le prove, poi messa in servizio.</t>
+          <t>Se l'unità esterna va su un'altra facciata, il metro in più ha già un prezzo, fissato prima.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
+          <t>V.2</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Flessibile posato oltre la quantità di computo, con fascette e sostegni</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>nell'impianto: aria di mandata; solo prezzo unitario</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>regola Nove C per le varianti a prezzo unitario</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>Come sopra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>V.3</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione in corrugato oltre la quantità di computo, stessa sezione</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>nell'impianto: alimentazione elettrica; solo prezzo unitario</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>regola Nove C per le varianti a prezzo unitario</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>La posizione del quadro si conferma in sopralluogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>V.4</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Accesso aggiuntivo in cantiere (oltre i due previsti)</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>sempre; solo prezzo unitario</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>regola Nove C per le varianti a prezzo unitario</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Il prezzo a corpo vale per due accessi: posa con le prove, poi messa in servizio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
           <t>V.5</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>attivita/variante-centralino</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>nel grafo: electrical-panel; solo prezzo unitario</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>kit AA-01: lavoro/dimensionamento.py, VARIANTI V.5; REVISIONE-INDIPENDENTE.md rilievo 12</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Centralino aggiuntivo 8 moduli, se il quadro non ha i moduli liberi per le protezioni nuove</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>nell'impianto: Quadro elettrico; solo prezzo unitario</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>regola Nove C per le varianti a prezzo unitario</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>Lo spazio nel quadro esistente si vede solo in sopralluogo.</t>
         </is>
@@ -7466,7 +7615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7476,7 +7625,7 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Note, domande al progettista e avvisi</t>
+          <t>Note, cose da confermare, domande al progettista e avvisi</t>
         </is>
       </c>
     </row>
@@ -7540,31 +7689,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>La distinta non progetta: lunghezze, sezioni, portate, protezioni, marca e modello sono dati del progettista; la distinta li maggiora e ne conta il corredo con regole scritte, ciascuna con la sua fonte (regole cfc42a99c0fd0a1a).</t>
+          <t>Fornitura da confermare: apparecchiature fornite da Nove C; bocchette e griglie, opere edili del Committente; messa in servizio con Nove C.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>DA DEFINIRE</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>T03 (Mandata aria alle zone: PLZ-01 - B3): quanto e' lungo? Serve `lunghezza_m` (la lunghezza stimata) su una sua tubazione, o 0 se e' un raccordo diretto.</t>
+          <t>La distinta non progetta: lunghezze, sezioni, portate, protezioni, marca e modello sono dati del progettista; la distinta li maggiora e ne conta il corredo con regole scritte, ciascuna con la sua fonte (regole 198e12d3f9a4df09).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>DA DEFINIRE</t>
+          <t>Da confermare</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>T08: su UE-01 servono `precarica_fino_a_m`, `carica_aggiuntiva_g_m` e `refrigerante` (dati di macchina del progettista) per la riserva di refrigerante.</t>
+          <t>Fornitura: apparecchiature fornite da Nove C; bocchette e griglie del Committente; opere edili del Committente; messa in servizio con Nove C — come da regole predefinite di Nove C; confermare per questa offerta.</t>
         </is>
       </c>
     </row>
@@ -7576,31 +7725,31 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>T11 (Alimentazione centrale Airzone): manca `protezione` sul tratto.</t>
+          <t>T03 (Mandata aria alle zone: PLZ-01 - B3): quanto e' lungo? Serve `lunghezza_m` (la lunghezza stimata) su una sua tubazione, o 0 se e' un raccordo diretto.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Avviso</t>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>T09 (Scarico condensa: UI-01 - SIF-01 - scarico): c-2 senza lunghezza; si considera compresa nei 7,6 m dati sul tratto.</t>
+          <t>T08: su UE-01 servono `precarica_fino_a_m` e `carica_aggiuntiva_g_m` (dati di macchina del progettista) per la riserva di refrigerante.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Avviso</t>
+          <t>DA DEFINIRE</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>T10 (Alimentazione unita' esterna: UE-01 - SZ-01 - QE-01): e-1a senza lunghezza; si considera compresa nei 15 m dati sul tratto.</t>
+          <t>T11 (Alimentazione centrale Airzone): manca `protezione` sul tratto.</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7761,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>T02, T04, T05 (aria di mandata): attraversamenti di parete non dati, assunti 1 per tratto (kit AA-01: lavoro/dimensionamento.py, voce F «Foratura di tramezza … n 7: 5 bocchette e 2 nella tramezza fra i disimpegni»).</t>
+          <t>T09 (Scarico condensa: UI-01 - SIF-01 - AL-01): la tubazione SIF-01 - AL-01 senza lunghezza; si considera compresa nei 7,6 m dati sul tratto.</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7773,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>T09 (condensa): attraversamenti di parete non dati, assunti 1 per tratto (kit AA-01: lavoro/dimensionamento.py, voce F.4 «Foratura per la condensa verso il bagno»).</t>
+          <t>T10 (Alimentazione unita' esterna: QE-01 - SZ-01 - UE-01): la tubazione SZ-01 - UE-01 senza lunghezza; si considera compresa nei 15 m dati sul tratto.</t>
         </is>
       </c>
     </row>
@@ -7635,6 +7784,30 @@
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>T02, T04, T05 (aria di mandata): attraversamenti di parete non dati, assunti 1 per tratto (regola Nove C: una parete per ramo, se il progettista non dice quante).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Avviso</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>T09 (condensa): attraversamenti di parete non dati, assunti 1 per tratto (regola Nove C: una parete, se il progettista non dice quante).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Avviso</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>T13, scritta sulla tavola: «P1-P2 · L 3 m», contro L 5 m da quotare.</t>
         </is>

--- a/docs/collaudi/REL-013/AA-01-con-dati-mancanti/distinta.xlsx
+++ b/docs/collaudi/REL-013/AA-01-con-dati-mancanti/distinta.xlsx
@@ -612,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Committente: Committente (dati omessi). Indirizzo: Indirizzo omesso. Allegata alla tavola M.02, rev. 00 del 29.10.2026. Regole della distinta 198e12d3f9a4df09. Quantità indicative.</t>
+          <t>Committente: Committente (dati omessi). Indirizzo: Indirizzo omesso. Allegata alla tavola M.02, rev. 00 del 29.10.2026. Regole della distinta f8b849f909489495. Quantità indicative.</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
+          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>T10 stimati 15 m</t>
+          <t>T10 stimati 12 m</t>
         </is>
       </c>
       <c r="G51" s="11" t="n"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
+          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>T11 stimati 12 m</t>
+          <t>T11 stimati 15 m</t>
         </is>
       </c>
       <c r="G52" s="11" t="n"/>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
+          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
+          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
+          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>T13 stimati 1,5 m; T14 stimati 3,7 m</t>
+          <t>T13 stimati 6,5 m; T14 stimati 4,9 m; T15 stimati 5,2 m; T16 stimati 3,7 m</t>
         </is>
       </c>
       <c r="G58" s="11" t="n"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
+          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>T15 stimati 6,5 m; T16 stimati 4,9 m; T17 stimati 5,2 m; T18 stimati 3,7 m</t>
+          <t>T17 stimati 3,7 m; T18 stimati 1,5 m</t>
         </is>
       </c>
       <c r="G59" s="11" t="n"/>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>canale di ripresa coibentato</t>
+          <t>plenum di ripresa coibentato</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
@@ -3999,17 +3999,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Alimentazione unita' esterna</t>
+          <t>Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>QE-01 - SZ-01 - UE-01</t>
+          <t>QE-01 - CZ-01</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>3G2,5</t>
+          <t>3G1,5</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -4020,14 +4020,14 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>20</v>
-      </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>(15 + 1) × 1,15 = 18,4 → 18,5 m; minimo scritto sul tratto 20 m → 20 m</t>
+          <t>(12 + 1) × 1,15 = 14,95 → 15 m</t>
         </is>
       </c>
     </row>
@@ -4039,17 +4039,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Alimentazione centrale Airzone</t>
+          <t>Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>QE-01 - CZ-01</t>
+          <t>QE-01 - SZ-01 - UE-01</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>3G1,5</t>
+          <t>3G2,5</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -4060,14 +4060,14 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>(12 + 1) × 1,15 = 14,95 → 15 m</t>
+          <t>(15 + 1) × 1,15 = 18,4 → 18,5 m; minimo scritto sul tratto 20 m → 20 m</t>
         </is>
       </c>
     </row>
@@ -4119,17 +4119,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Linea P1-P2 dell'unita' interna</t>
+          <t>Bus Airzone ai termostati</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>UI-01 - CZ-01</t>
+          <t>CZ-01 - TZ-01</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2×0,75 (P1-P2)</t>
+          <t>bus Airzone, schermato</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -4140,14 +4140,14 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>(1,5 + 1) × 1,15 = 2,88 → 3 m; minimo bus 5 m → 5 m</t>
+          <t>(6,5 + 1) × 1,15 = 8,62 → 9 m</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Linea P1-P2 dell'unita' interna</t>
+          <t>Bus Airzone ai termostati</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>UI-01 - CF-01</t>
+          <t>CZ-01 - TZ-02</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2×0,75 (P1-P2)</t>
+          <t>bus Airzone, schermato</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -4180,14 +4180,14 @@
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>(3,7 + 1) × 1,15 = 5,4 → 5,5 m</t>
+          <t>(4,9 + 1) × 1,15 = 6,79 → 7 m</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>CZ-01 - TZ-01</t>
+          <t>CZ-01 - TZ-03</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -4220,14 +4220,14 @@
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>(6,5 + 1) × 1,15 = 8,62 → 9 m</t>
+          <t>(5,2 + 1) × 1,15 = 7,13 → 7,5 m</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>CZ-01 - TZ-02</t>
+          <t>CZ-01 - TZ-04</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4260,14 +4260,14 @@
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>(4,9 + 1) × 1,15 = 6,79 → 7 m</t>
+          <t>(3,7 + 1) × 1,15 = 5,4 → 5,5 m</t>
         </is>
       </c>
     </row>
@@ -4279,17 +4279,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bus Airzone ai termostati</t>
+          <t>Linea P1-P2 dell'unita' interna</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>CZ-01 - TZ-03</t>
+          <t>UI-01 - CF-01</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>bus Airzone, schermato</t>
+          <t>2×0,75 (P1-P2)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -4300,14 +4300,14 @@
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>(5,2 + 1) × 1,15 = 7,13 → 7,5 m</t>
+          <t>(3,7 + 1) × 1,15 = 5,4 → 5,5 m</t>
         </is>
       </c>
     </row>
@@ -4319,17 +4319,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Bus Airzone ai termostati</t>
+          <t>Linea P1-P2 dell'unita' interna</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>CZ-01 - TZ-04</t>
+          <t>UI-01 - CZ-01</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>bus Airzone, schermato</t>
+          <t>2×0,75 (P1-P2)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -4340,14 +4340,14 @@
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>(3,7 + 1) × 1,15 = 5,4 → 5,5 m</t>
+          <t>(1,5 + 1) × 1,15 = 2,88 → 3 m; minimo bus 5 m → 5 m</t>
         </is>
       </c>
     </row>
@@ -5033,12 +5033,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>«3G2,5 · L 20 m»</t>
+          <t>«3G1,5 · L 15 m»</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>L 20 m da quotare</t>
+          <t>L 15 m da quotare</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>«3G1,5 · L 15 m»</t>
+          <t>«3G2,5 · L 20 m»</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>L 15 m da quotare</t>
+          <t>L 20 m da quotare</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -5129,17 +5129,17 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>«P1-P2 · L 3 m»</t>
+          <t>«bus · L 9 m»</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>L 5 m da quotare</t>
+          <t>L 9 m da quotare</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>oltre</t>
+          <t>entro</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>«P1-P2 · L 5,5 m»</t>
+          <t>«bus · L 7 m»</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>L 5,5 m da quotare</t>
+          <t>L 7 m da quotare</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 9 m»</t>
+          <t>«bus · L 7,5 m»</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>L 9 m da quotare</t>
+          <t>L 7,5 m da quotare</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 7 m»</t>
+          <t>«bus · L 5,5 m»</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>L 7 m da quotare</t>
+          <t>L 5,5 m da quotare</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 7,5 m»</t>
+          <t>«P1-P2 · L 5,5 m»</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>L 7,5 m da quotare</t>
+          <t>L 5,5 m da quotare</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>«bus · L 5,5 m»</t>
+          <t>«P1-P2 · L 3 m»</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>L 5,5 m da quotare</t>
+          <t>L 5 m da quotare</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>entro</t>
+          <t>oltre</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
+          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>T10 20 m</t>
+          <t>T10 15 m</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Cavo FG16OR16 3G1,5, Alimentazione centrale Airzone</t>
+          <t>Cavo FG16OR16 3G2,5, Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>T11 15 m</t>
+          <t>T11 20 m</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
+          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>DA DEFINIRE (protezione), linea dedicata: Alimentazione centrale Airzone</t>
+          <t>Magnetotermico-differenziale 1P+N C16, Idn 30 mA, tipo A o F, 6 kA, linea dedicata: Alimentazione unita' esterna</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>T10 20 + T11 15 = 35 m × 1, per eccesso a 10 m = 40 m</t>
+          <t>T10 15 + T11 20 = 35 m × 1, per eccesso a 10 m = 40 m</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
+          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>T13 5 + T14 5,5 = 10,5 m</t>
+          <t>T13 9 + T14 7 + T15 7,5 + T16 5,5 = 29 m</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cavo bus Airzone, schermato, Bus Airzone ai termostati</t>
+          <t>Cavo 2×0,75 (P1-P2), Linea P1-P2 dell'unita' interna</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>T15 9 + T16 7 + T17 7,5 + T18 5,5 = 29 m</t>
+          <t>T17 5,5 + T18 5 = 10,5 m</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>T13 5 + T14 5,5 + T15 9 + T16 7 + T17 7,5 + T18 5,5 = 39,5 m × 1, per eccesso a 10 m = 40 m</t>
+          <t>T13 9 + T14 7 + T15 7,5 + T16 5,5 + T17 5,5 + T18 5 = 39,5 m × 1, per eccesso a 10 m = 40 m</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>La distinta non progetta: lunghezze, sezioni, portate, protezioni, marca e modello sono dati del progettista; la distinta li maggiora e ne conta il corredo con regole scritte, ciascuna con la sua fonte (regole 198e12d3f9a4df09).</t>
+          <t>La distinta non progetta: lunghezze, sezioni, portate, protezioni, marca e modello sono dati del progettista; la distinta li maggiora e ne conta il corredo con regole scritte, ciascuna con la sua fonte (regole f8b849f909489495).</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>T11 (Alimentazione centrale Airzone): manca `protezione` sul tratto.</t>
+          <t>T10 (Alimentazione centrale Airzone): manca `protezione` sul tratto.</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>T10 (Alimentazione unita' esterna: QE-01 - SZ-01 - UE-01): la tubazione SZ-01 - UE-01 senza lunghezza; si considera compresa nei 15 m dati sul tratto.</t>
+          <t>T11 (Alimentazione unita' esterna: QE-01 - SZ-01 - UE-01): la tubazione SZ-01 - UE-01 senza lunghezza; si considera compresa nei 15 m dati sul tratto.</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>T13, scritta sulla tavola: «P1-P2 · L 3 m», contro L 5 m da quotare.</t>
+          <t>T18, scritta sulla tavola: «P1-P2 · L 3 m», contro L 5 m da quotare.</t>
         </is>
       </c>
     </row>
